--- a/DEV/org.openl.rules.test/test-resources/functionality/Math.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/Math.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vpikus/Sources/OpenL/openl-tablets/DEV/org.openl.rules.test/test-resources/functionality/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF0288A-3958-524F-905C-397DB91FE7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C900D3-D862-3B4A-B111-F9CC5C08B033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34980" windowHeight="22600" tabRatio="765" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34980" windowHeight="22600" tabRatio="765" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="X" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
             <charset val="204"/>
@@ -71,18 +71,28 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
-http://openl-tablets.sourceforge.net/docs/openl-tablets/latest/OpenL%20Tablets%20-%20Reference%20Guide/index.html
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">http://openl-tablets.sourceforge.net/docs/openl-tablets/latest/OpenL%20Tablets%20-%20Reference%20Guide/index.html
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="C80" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
+    <comment ref="D80" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
       <text>
         <r>
           <rPr>
@@ -108,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E85" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000003000000}">
+    <comment ref="F85" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000003000000}">
       <text>
         <r>
           <rPr>
@@ -132,32 +142,6 @@
           <t xml:space="preserve">
 http://openl-tablets.sourceforge.net/docs/openl-tablets/latest/OpenL%20Tablets%20-%20Reference%20Guide/index.html
 </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Polina Kaziuchyts:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-roundingMethod 7 (ROUND_UNNECESSARY) is not working</t>
         </r>
       </text>
     </comment>
@@ -384,55 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Polina Kaziuchyts:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Д. Левчук: деление на 0 для Double должно возвращать Infinity</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Polina Kaziuchyts:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Д. Левчук: деление на 0 для Double должно возвращать Infinity</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
       <text>
         <r>
           <rPr>
@@ -456,31 +392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Polina Kaziuchyts:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Число для проверки отсутствует. В таком случае можн было бы возвращать ошибку или Empty</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000006000000}">
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000005000000}">
       <text>
         <r>
           <rPr>
@@ -509,7 +421,31 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Производится деление не на ноль, а на пустой элемент, в таком случае было бы логично вернуть подаваемое число без изменений</t>
+          <t>Число для проверки отсутствует. В таком случае можн было бы возвращать ошибку или Empty</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Polina Kaziuchyts:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Производится деление не на ноль, а на пустой элемент, в таком случае было бы логично вернуть подаваемое число без изменений</t>
         </r>
       </text>
     </comment>
@@ -546,12 +482,78 @@
         </r>
       </text>
     </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Polina Kaziuchyts:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Д. Левчук: деление на 0 для Double должно возвращать Infinity</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Polina Kaziuchyts:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Д. Левчук: деление на 0 для Double должно возвращать Infinity</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="321">
   <si>
     <t>_res_</t>
   </si>
@@ -1342,175 +1344,178 @@
     <t>Method Double IEEEremainderMethod (Double x, Double y)</t>
   </si>
   <si>
+    <t>Test IEEEremainderMethod IEEEremainderTest</t>
+  </si>
+  <si>
+    <t>0.9900000000000091</t>
+  </si>
+  <si>
+    <t>0.9797787438470209</t>
+  </si>
+  <si>
+    <t>-0.1352212561529882</t>
+  </si>
+  <si>
+    <t>0.009999999999990905</t>
+  </si>
+  <si>
+    <t>-0.009999999999990905</t>
+  </si>
+  <si>
+    <t>Method Double roundMethod (Double a)</t>
+  </si>
+  <si>
+    <t>return round(a);</t>
+  </si>
+  <si>
+    <t>Test roundMethod roundTest</t>
+  </si>
+  <si>
+    <t>Test roundMethod_scale round_scaleTest</t>
+  </si>
+  <si>
+    <t>Method Double roundMethod_scale (Double a, int scale, int roundingMethod)</t>
+  </si>
+  <si>
+    <t>return round(a, scale, roundingMethod);</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>roundingMethod</t>
+  </si>
+  <si>
+    <t>Test quotientMethod quotientTest</t>
+  </si>
+  <si>
+    <t>Method Double quotientMethod (Double number, Double divisor)</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>return quotient(number, divisor);</t>
+  </si>
+  <si>
+    <t>divisor</t>
+  </si>
+  <si>
+    <t>Method Double modMethod (Double number, Double divisor)</t>
+  </si>
+  <si>
+    <t>return mod(number, divisor);</t>
+  </si>
+  <si>
+    <t>Test modMethod modTest</t>
+  </si>
+  <si>
+    <t>return random();</t>
+  </si>
+  <si>
+    <t>Method Double randomMethod()</t>
+  </si>
+  <si>
+    <t>return format(a, fmt);</t>
+  </si>
+  <si>
+    <t>return format(a);</t>
+  </si>
+  <si>
+    <t>Test formatMethod formatTest</t>
+  </si>
+  <si>
+    <t>fmt</t>
+  </si>
+  <si>
+    <t>#0.0000</t>
+  </si>
+  <si>
+    <t>1.0000</t>
+  </si>
+  <si>
+    <t>180.0000</t>
+  </si>
+  <si>
+    <t>-180.0000</t>
+  </si>
+  <si>
+    <t>361.0000</t>
+  </si>
+  <si>
+    <t>0.0000</t>
+  </si>
+  <si>
+    <t>0.0100</t>
+  </si>
+  <si>
+    <t>360.9898</t>
+  </si>
+  <si>
+    <t>360.0100</t>
+  </si>
+  <si>
+    <t>-360.0100</t>
+  </si>
+  <si>
+    <t>#0.5793</t>
+  </si>
+  <si>
+    <t>1.5793</t>
+  </si>
+  <si>
+    <t>180.5793</t>
+  </si>
+  <si>
+    <t>-180.5793</t>
+  </si>
+  <si>
+    <t>361.5793</t>
+  </si>
+  <si>
+    <t>0.5793</t>
+  </si>
+  <si>
+    <t>360.5793</t>
+  </si>
+  <si>
+    <t>-360.5793</t>
+  </si>
+  <si>
+    <t>#0.1232</t>
+  </si>
+  <si>
+    <t>361.1232</t>
+  </si>
+  <si>
+    <t>Test randomMethod randomMethodTest</t>
+  </si>
+  <si>
+    <t>Method String formatMethod (Double a)</t>
+  </si>
+  <si>
+    <t>Method String formatMethod_formatter (Double a, String fmt)</t>
+  </si>
+  <si>
+    <t>360.98977874</t>
+  </si>
+  <si>
+    <t>5.9685512897846565E156</t>
+  </si>
+  <si>
+    <t>_description_</t>
+  </si>
+  <si>
     <t>return IEEEremainder(x, y);</t>
   </si>
   <si>
-    <t>Test IEEEremainderMethod IEEEremainderTest</t>
-  </si>
-  <si>
-    <t>0.9900000000000091</t>
-  </si>
-  <si>
-    <t>0.9797787438470209</t>
-  </si>
-  <si>
-    <t>-0.1352212561529882</t>
-  </si>
-  <si>
-    <t>0.009999999999990905</t>
-  </si>
-  <si>
-    <t>-0.009999999999990905</t>
-  </si>
-  <si>
-    <t>Method Double roundMethod (Double a)</t>
-  </si>
-  <si>
-    <t>return round(a);</t>
-  </si>
-  <si>
-    <t>Test roundMethod roundTest</t>
-  </si>
-  <si>
-    <t>Test roundMethod_scale round_scaleTest</t>
-  </si>
-  <si>
-    <t>Method Double roundMethod_scale (Double a, int scale, int roundingMethod)</t>
-  </si>
-  <si>
-    <t>return round(a, scale, roundingMethod);</t>
-  </si>
-  <si>
-    <t>scale</t>
-  </si>
-  <si>
-    <t>roundingMethod</t>
-  </si>
-  <si>
-    <t>Test quotientMethod quotientTest</t>
-  </si>
-  <si>
-    <t>Method Double quotientMethod (Double number, Double divisor)</t>
-  </si>
-  <si>
-    <t>number</t>
-  </si>
-  <si>
-    <t>return quotient(number, divisor);</t>
-  </si>
-  <si>
-    <t>divisor</t>
-  </si>
-  <si>
-    <t>Method Double modMethod (Double number, Double divisor)</t>
-  </si>
-  <si>
-    <t>return mod(number, divisor);</t>
-  </si>
-  <si>
-    <t>Test modMethod modTest</t>
-  </si>
-  <si>
-    <t>-0.876277657019125</t>
-  </si>
-  <si>
-    <t>return random();</t>
-  </si>
-  <si>
-    <t>Method Double randomMethod()</t>
-  </si>
-  <si>
-    <t>return format(a, fmt);</t>
-  </si>
-  <si>
-    <t>return format(a);</t>
-  </si>
-  <si>
-    <t>Test formatMethod formatTest</t>
-  </si>
-  <si>
-    <t>fmt</t>
-  </si>
-  <si>
-    <t>#0.0000</t>
-  </si>
-  <si>
-    <t>1.0000</t>
-  </si>
-  <si>
-    <t>180.0000</t>
-  </si>
-  <si>
-    <t>-180.0000</t>
-  </si>
-  <si>
-    <t>361.0000</t>
-  </si>
-  <si>
-    <t>0.0000</t>
-  </si>
-  <si>
-    <t>0.0100</t>
-  </si>
-  <si>
-    <t>360.9898</t>
-  </si>
-  <si>
-    <t>360.0100</t>
-  </si>
-  <si>
-    <t>-360.0100</t>
-  </si>
-  <si>
-    <t>#0.5793</t>
-  </si>
-  <si>
-    <t>1.5793</t>
-  </si>
-  <si>
-    <t>180.5793</t>
-  </si>
-  <si>
-    <t>-180.5793</t>
-  </si>
-  <si>
-    <t>361.5793</t>
-  </si>
-  <si>
-    <t>0.5793</t>
-  </si>
-  <si>
-    <t>360.5793</t>
-  </si>
-  <si>
-    <t>-360.5793</t>
-  </si>
-  <si>
-    <t>#0.1232</t>
-  </si>
-  <si>
-    <t>361.1232</t>
-  </si>
-  <si>
-    <t>Test randomMethod randomMethodTest</t>
-  </si>
-  <si>
-    <t>0.989778743847</t>
-  </si>
-  <si>
-    <t>Method String formatMethod (Double a)</t>
-  </si>
-  <si>
-    <t>Method String formatMethod_formatter (Double a, String fmt)</t>
-  </si>
-  <si>
-    <t>360.98977874</t>
-  </si>
-  <si>
-    <t>5.9685512897846565E156</t>
-  </si>
-  <si>
-    <t>_description_</t>
+    <t>0.9897787438470118</t>
+  </si>
+  <si>
+    <t>7.010221256152988</t>
+  </si>
+  <si>
+    <t>-7.010221256152988</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1532,7 @@
     <numFmt numFmtId="170" formatCode="0.000000000000"/>
     <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1595,8 +1600,88 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF5A5A5A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1606,12 +1691,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="46"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="55"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1627,8 +1706,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6DCE5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1788,17 +1903,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1826,10 +1930,89 @@
     </border>
     <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9BC2E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9BC2E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
+      <bottom style="thin">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9BC2E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9BC2E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9BC2E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9BC2E6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BC2E6"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1837,7 +2020,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1858,7 +2041,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1882,40 +2064,97 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2360,22 +2599,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -2397,7 +2636,7 @@
       <c r="B8" s="19">
         <v>1</v>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="45">
         <v>0.8414709848078965</v>
       </c>
     </row>
@@ -2405,7 +2644,7 @@
       <c r="B9" s="19">
         <v>180</v>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="45">
         <v>-0.80115263573383044</v>
       </c>
     </row>
@@ -2413,7 +2652,7 @@
       <c r="B10" s="19">
         <v>-180</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="45">
         <v>0.80115263573383044</v>
       </c>
     </row>
@@ -2421,7 +2660,7 @@
       <c r="B11" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="45">
         <v>0.27938655435956988</v>
       </c>
     </row>
@@ -2429,7 +2668,7 @@
       <c r="B12" s="19">
         <v>0</v>
       </c>
-      <c r="C12" s="57">
+      <c r="C12" s="45">
         <v>0</v>
       </c>
     </row>
@@ -2437,7 +2676,7 @@
       <c r="B13" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="45">
         <v>9.9998333341666645E-3</v>
       </c>
     </row>
@@ -2445,7 +2684,7 @@
       <c r="B14" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="57">
+      <c r="C14" s="45">
         <v>0.28918602180993719</v>
       </c>
     </row>
@@ -2453,7 +2692,7 @@
       <c r="B15" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="45">
         <v>0.95603091439443222</v>
       </c>
     </row>
@@ -2461,27 +2700,27 @@
       <c r="B16" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="58">
+      <c r="C16" s="46">
         <v>-0.95603091439443222</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="76"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="77"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="75"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -2503,7 +2742,7 @@
       <c r="B26" s="6">
         <v>1</v>
       </c>
-      <c r="C26" s="57">
+      <c r="C26" s="45">
         <v>0.54030230586813977</v>
       </c>
     </row>
@@ -2511,7 +2750,7 @@
       <c r="B27" s="6">
         <v>180</v>
       </c>
-      <c r="C27" s="57">
+      <c r="C27" s="45">
         <v>-0.59846006905785809</v>
       </c>
     </row>
@@ -2519,15 +2758,15 @@
       <c r="B28" s="6">
         <v>-180</v>
       </c>
-      <c r="C28" s="57">
+      <c r="C28" s="45">
         <v>-0.59846006905785809</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>361</v>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="45">
         <v>-0.96017870901363311</v>
       </c>
     </row>
@@ -2535,7 +2774,7 @@
       <c r="B30" s="6">
         <v>0</v>
       </c>
-      <c r="C30" s="57">
+      <c r="C30" s="45">
         <v>1</v>
       </c>
     </row>
@@ -2543,59 +2782,59 @@
       <c r="B31" s="6">
         <v>0.01</v>
       </c>
-      <c r="C31" s="57">
+      <c r="C31" s="45">
         <v>0.99995000041666526</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>360.98977874384701</v>
       </c>
-      <c r="C32" s="57">
+      <c r="C32" s="45">
         <v>-0.95727292074399684</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>360.01</v>
       </c>
-      <c r="C33" s="57">
+      <c r="C33" s="45">
         <v>-0.29326590446580347</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>-360.01</v>
       </c>
-      <c r="C34" s="57">
+      <c r="C34" s="45">
         <v>-0.29326590446580347</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B35" s="28">
+      <c r="B35" s="27">
         <v>0.73908513321516101</v>
       </c>
-      <c r="C35" s="58">
+      <c r="C35" s="46">
         <v>0.73908513321516045</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="61" t="s">
+      <c r="B39" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="61"/>
+      <c r="C39" s="76"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B40" s="62" t="s">
+      <c r="B40" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="62"/>
+      <c r="C40" s="77"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B42" s="63" t="s">
+      <c r="B42" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="65"/>
+      <c r="C42" s="75"/>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B43" s="4" t="s">
@@ -2614,10 +2853,10 @@
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B45" s="28">
-        <v>1</v>
-      </c>
-      <c r="C45" s="57">
+      <c r="B45" s="27">
+        <v>1</v>
+      </c>
+      <c r="C45" s="45">
         <v>1.5574077246549023</v>
       </c>
     </row>
@@ -2625,7 +2864,7 @@
       <c r="B46" s="6">
         <v>180</v>
       </c>
-      <c r="C46" s="57">
+      <c r="C46" s="45">
         <v>1.3386902103511544</v>
       </c>
     </row>
@@ -2633,15 +2872,15 @@
       <c r="B47" s="6">
         <v>-180</v>
       </c>
-      <c r="C47" s="57">
+      <c r="C47" s="45">
         <v>-1.3386902103511544</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B48" s="28">
+      <c r="B48" s="27">
         <v>361</v>
       </c>
-      <c r="C48" s="57">
+      <c r="C48" s="45">
         <v>-0.29097349455558802</v>
       </c>
     </row>
@@ -2649,23 +2888,23 @@
       <c r="B49" s="6">
         <v>0</v>
       </c>
-      <c r="C49" s="57">
+      <c r="C49" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B50" s="28">
+      <c r="B50" s="27">
         <v>0.01</v>
       </c>
-      <c r="C50" s="57">
+      <c r="C50" s="45">
         <v>1.0000333346667207E-2</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B51" s="28">
+      <c r="B51" s="27">
         <v>360.98977874384701</v>
       </c>
-      <c r="C51" s="57">
+      <c r="C51" s="45">
         <v>-0.30209359895522842</v>
       </c>
     </row>
@@ -2673,15 +2912,15 @@
       <c r="B52" s="6">
         <v>360.01</v>
       </c>
-      <c r="C52" s="57">
+      <c r="C52" s="45">
         <v>-3.2599456664963626</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B53" s="28">
+      <c r="B53" s="27">
         <v>-360.01</v>
       </c>
-      <c r="C53" s="58">
+      <c r="C53" s="46">
         <v>3.2599456664963626</v>
       </c>
     </row>
@@ -2704,401 +2943,479 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="B2:E42"/>
+  <dimension ref="B2:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="3" width="21.5" customWidth="1"/>
-    <col min="4" max="4" width="26.5" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+    <row r="2" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="70" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+    </row>
+    <row r="3" spans="2:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="72" t="s">
         <v>283</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B5" s="68" t="s">
         <v>284</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
-        <v>285</v>
-      </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B6" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B7" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B8" s="6">
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B6" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B7" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B8" s="49">
+        <v>1</v>
+      </c>
+      <c r="C8" s="49">
         <v>25</v>
       </c>
-      <c r="C8" s="6">
+      <c r="D8" s="49">
         <v>5</v>
       </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B9" s="6">
+      <c r="E8" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B9" s="50">
+        <v>2</v>
+      </c>
+      <c r="C9" s="50">
         <v>25</v>
       </c>
-      <c r="C9" s="28">
+      <c r="D9" s="51">
         <v>4</v>
       </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B10" s="6"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B11" s="51">
-        <v>1</v>
+      <c r="E9" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B10" s="49">
+        <v>3</v>
+      </c>
+      <c r="C10" s="49"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="49"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B11" s="50">
+        <v>4</v>
       </c>
       <c r="C11" s="50">
-        <v>0</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B12" s="52">
-        <v>1</v>
-      </c>
-      <c r="C12" s="50">
-        <v>0</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B13" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="51">
+        <v>0</v>
+      </c>
+      <c r="E11" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B12" s="49">
+        <v>5</v>
+      </c>
+      <c r="C12" s="53">
+        <v>1</v>
+      </c>
+      <c r="D12" s="52">
+        <v>0</v>
+      </c>
+      <c r="E12" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B13" s="50">
+        <v>6</v>
+      </c>
+      <c r="C13" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="28">
+      <c r="D13" s="51">
         <v>8</v>
       </c>
-      <c r="D13" s="56" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B14" s="28">
+      <c r="E13" s="55" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B14" s="49">
+        <v>7</v>
+      </c>
+      <c r="C14" s="52">
         <v>360</v>
       </c>
-      <c r="C14" s="28">
+      <c r="D14" s="52">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B15" s="6">
+      <c r="E14" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B15" s="50">
+        <v>8</v>
+      </c>
+      <c r="C15" s="50">
         <v>-360</v>
       </c>
-      <c r="C15" s="28">
+      <c r="D15" s="51">
         <v>8</v>
       </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B16" s="14" t="s">
+      <c r="E15" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B16" s="49">
+        <v>9</v>
+      </c>
+      <c r="C16" s="56" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="28">
+      <c r="D16" s="52">
         <v>8</v>
       </c>
-      <c r="D16" s="53" t="s">
-        <v>286</v>
+      <c r="E16" s="66" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="50">
+        <v>10</v>
+      </c>
+      <c r="C17" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="28">
+      <c r="D17" s="51">
         <v>-8</v>
       </c>
-      <c r="D17" s="53" t="s">
-        <v>286</v>
+      <c r="E17" s="67" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B18" s="28">
+      <c r="B18" s="49">
+        <v>11</v>
+      </c>
+      <c r="C18" s="52">
         <v>360</v>
       </c>
-      <c r="C18" s="28">
+      <c r="D18" s="52">
         <v>-8</v>
       </c>
-      <c r="D18" s="6">
+      <c r="E18" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B19" s="50">
+        <v>12</v>
+      </c>
+      <c r="C19" s="51">
         <v>360</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="50">
+      <c r="D19" s="50"/>
+      <c r="E19" s="51"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B20" s="49">
+        <v>13</v>
+      </c>
+      <c r="C20" s="49"/>
+      <c r="D20" s="52">
+        <v>5</v>
+      </c>
+      <c r="E20" s="49"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B21" s="50">
+        <v>14</v>
+      </c>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+    </row>
+    <row r="25" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="70" t="s">
+        <v>278</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+    </row>
+    <row r="26" spans="2:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="72" t="s">
+        <v>280</v>
+      </c>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B28" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B29" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="D29" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B30" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="C30" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="D30" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="E30" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B31" s="49">
+        <v>1</v>
+      </c>
+      <c r="C31" s="49">
+        <v>25</v>
+      </c>
+      <c r="D31" s="49">
+        <v>5</v>
+      </c>
+      <c r="E31" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B32" s="50">
+        <v>2</v>
+      </c>
+      <c r="C32" s="50">
+        <v>25</v>
+      </c>
+      <c r="D32" s="51">
+        <v>4</v>
+      </c>
+      <c r="E32" s="50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B33" s="49">
+        <v>3</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="52">
+        <v>8</v>
+      </c>
+      <c r="E33" s="49">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B34" s="50">
+        <v>4</v>
+      </c>
+      <c r="C34" s="51">
         <v>360</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B20" s="51"/>
-      <c r="C20" s="50">
+      <c r="D34" s="51">
+        <v>8</v>
+      </c>
+      <c r="E34" s="50">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B35" s="49">
         <v>5</v>
       </c>
-      <c r="D20" s="51"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B25" s="61" t="s">
-        <v>279</v>
-      </c>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B26" s="62" t="s">
-        <v>281</v>
-      </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B28" s="59" t="s">
-        <v>278</v>
-      </c>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B29" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B30" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B31" s="6">
-        <v>1</v>
-      </c>
-      <c r="C31" s="6">
-        <v>25</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C35" s="49">
+        <v>-360</v>
+      </c>
+      <c r="D35" s="52">
+        <v>8</v>
+      </c>
+      <c r="E35" s="49">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B36" s="50">
+        <v>6</v>
+      </c>
+      <c r="C36" s="54" t="s">
+        <v>197</v>
+      </c>
+      <c r="D36" s="51">
+        <v>8</v>
+      </c>
+      <c r="E36" s="50">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B37" s="49">
+        <v>7</v>
+      </c>
+      <c r="C37" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="52">
+        <v>-8</v>
+      </c>
+      <c r="E37" s="49">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B38" s="50">
+        <v>8</v>
+      </c>
+      <c r="C38" s="51">
+        <v>360</v>
+      </c>
+      <c r="D38" s="51">
+        <v>-8</v>
+      </c>
+      <c r="E38" s="50">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B39" s="49">
+        <v>9</v>
+      </c>
+      <c r="C39" s="49"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="65"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B40" s="50">
+        <v>10</v>
+      </c>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="50"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B41" s="49">
+        <v>11</v>
+      </c>
+      <c r="C41" s="52">
+        <v>360</v>
+      </c>
+      <c r="D41" s="49"/>
+      <c r="E41" s="52"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B42" s="50">
+        <v>12</v>
+      </c>
+      <c r="C42" s="50"/>
+      <c r="D42" s="51">
         <v>5</v>
       </c>
-      <c r="E31" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B32" s="6">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>25</v>
-      </c>
-      <c r="D32" s="28">
-        <v>4</v>
-      </c>
-      <c r="E32" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B33" s="6">
-        <v>3</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="28">
-        <v>8</v>
-      </c>
-      <c r="E33" s="6">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B34" s="6">
-        <v>4</v>
-      </c>
-      <c r="C34" s="28">
-        <v>360</v>
-      </c>
-      <c r="D34" s="28">
-        <v>8</v>
-      </c>
-      <c r="E34" s="6">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B35" s="6">
-        <v>5</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-360</v>
-      </c>
-      <c r="D35" s="28">
-        <v>8</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B36" s="6">
-        <v>6</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D36" s="28">
-        <v>8</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B37" s="6">
-        <v>7</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="28">
-        <v>-8</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B38" s="6">
-        <v>8</v>
-      </c>
-      <c r="C38" s="28">
-        <v>360</v>
-      </c>
-      <c r="D38" s="28">
-        <v>-8</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B39" s="6">
-        <v>9</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B40" s="6">
-        <v>10</v>
-      </c>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B41" s="51">
-        <v>11</v>
-      </c>
-      <c r="C41" s="50">
-        <v>360</v>
-      </c>
-      <c r="D41" s="51"/>
-      <c r="E41" s="50"/>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B42" s="51">
-        <v>12</v>
-      </c>
-      <c r="C42" s="51"/>
-      <c r="D42" s="50">
-        <v>5</v>
-      </c>
-      <c r="E42" s="51"/>
+      <c r="E42" s="50"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B44" s="49">
+        <v>13</v>
+      </c>
+      <c r="C44" s="49">
+        <v>1</v>
+      </c>
+      <c r="D44" s="52">
+        <v>0</v>
+      </c>
+      <c r="E44" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B45" s="50">
+        <v>14</v>
+      </c>
+      <c r="C45" s="57">
+        <v>1</v>
+      </c>
+      <c r="D45" s="51">
+        <v>0</v>
+      </c>
+      <c r="E45" s="50" t="s">
+        <v>115</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3117,22 +3434,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>142</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -3154,7 +3471,7 @@
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="27" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3162,7 +3479,7 @@
       <c r="B9" s="6">
         <v>180</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="27" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3170,15 +3487,15 @@
       <c r="B10" s="6">
         <v>-180</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="27" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <v>361</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="27" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3186,7 +3503,7 @@
       <c r="B12" s="6">
         <v>0</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="27" t="s">
         <v>143</v>
       </c>
     </row>
@@ -3194,15 +3511,15 @@
       <c r="B13" s="6">
         <v>0.01</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="27" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>360.98977874384701</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3210,44 +3527,44 @@
       <c r="B15" s="6">
         <v>360.01</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="27" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>-360.01</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="76" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="77" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="65"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="75"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="24" t="s">
         <v>87</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -3258,7 +3575,7 @@
       <c r="B25" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D25" s="18" t="s">
@@ -3299,7 +3616,7 @@
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>361</v>
       </c>
       <c r="C29" s="6">
@@ -3332,7 +3649,7 @@
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C32" s="6">
@@ -3354,7 +3671,7 @@
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>-360.01</v>
       </c>
       <c r="C34" s="6">
@@ -3398,7 +3715,7 @@
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B38" s="28">
+      <c r="B38" s="27">
         <v>361</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3431,7 +3748,7 @@
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B41" s="28">
+      <c r="B41" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3453,7 +3770,7 @@
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B43" s="28">
+      <c r="B43" s="27">
         <v>-360.01</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3497,7 +3814,7 @@
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B47" s="28">
+      <c r="B47" s="27">
         <v>361</v>
       </c>
       <c r="C47" s="6">
@@ -3530,7 +3847,7 @@
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B50" s="28">
+      <c r="B50" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C50" s="6">
@@ -3552,7 +3869,7 @@
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B52" s="28">
+      <c r="B52" s="27">
         <v>-360.01</v>
       </c>
       <c r="C52" s="6">
@@ -3587,22 +3904,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>260</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>261</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -3624,16 +3941,16 @@
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="34">
-        <v>1</v>
-      </c>
-      <c r="D8" s="35"/>
+      <c r="C8" s="33">
+        <v>1</v>
+      </c>
+      <c r="D8" s="34"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B9" s="6">
         <v>180</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <v>180</v>
       </c>
     </row>
@@ -3641,16 +3958,16 @@
       <c r="B10" s="6">
         <v>-180</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="27">
         <v>180</v>
       </c>
       <c r="E10" s="16"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <v>361</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="27">
         <v>361</v>
       </c>
     </row>
@@ -3663,19 +3980,19 @@
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <v>0.47942553860420301</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="37">
         <v>0.47942553860420301</v>
       </c>
-      <c r="D13" s="32"/>
+      <c r="D13" s="31"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>360.98977874384701</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="38">
         <v>360.98977874384701</v>
       </c>
     </row>
@@ -3688,7 +4005,7 @@
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>-360.01</v>
       </c>
       <c r="C16" s="8">
@@ -3696,28 +4013,28 @@
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="76"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="77"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="75"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="22" t="s">
         <v>0</v>
       </c>
     </row>
@@ -3725,10 +4042,10 @@
       <c r="B25" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="33"/>
+      <c r="C25" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="32"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B26" s="6">
@@ -3737,7 +4054,7 @@
       <c r="C26" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="35"/>
+      <c r="E26" s="34"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B27" s="6">
@@ -3754,10 +4071,10 @@
       <c r="C28" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="36"/>
+      <c r="E28" s="35"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>361</v>
       </c>
       <c r="C29" s="14" t="s">
@@ -3773,7 +4090,7 @@
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>0.47942553860420301</v>
       </c>
       <c r="C31" s="14" t="s">
@@ -3781,7 +4098,7 @@
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C32" s="14" t="s">
@@ -3797,7 +4114,7 @@
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>-360.01</v>
       </c>
       <c r="C34" s="14" t="s">
@@ -3805,28 +4122,28 @@
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B37" s="61" t="s">
+      <c r="B37" s="76" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="61"/>
+      <c r="C37" s="76"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="62" t="s">
+      <c r="B38" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="62"/>
+      <c r="C38" s="77"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="65"/>
+      <c r="C40" s="75"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="22" t="s">
         <v>0</v>
       </c>
     </row>
@@ -3834,7 +4151,7 @@
       <c r="B42" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3863,7 +4180,7 @@
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B46" s="28">
+      <c r="B46" s="27">
         <v>361</v>
       </c>
       <c r="C46" s="14" t="s">
@@ -3879,7 +4196,7 @@
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B48" s="28">
+      <c r="B48" s="27">
         <v>0.47942553860420301</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -3887,7 +4204,7 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B49" s="28">
+      <c r="B49" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C49" s="14" t="s">
@@ -3903,7 +4220,7 @@
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B51" s="28">
+      <c r="B51" s="27">
         <v>-360.01</v>
       </c>
       <c r="C51" s="14" t="s">
@@ -3938,45 +4255,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="75"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="22" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="29" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3987,7 +4304,7 @@
       <c r="C8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="30" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3998,12 +4315,12 @@
       <c r="C9" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="30" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <v>-180</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -4014,7 +4331,7 @@
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>58</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -4025,7 +4342,7 @@
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <v>0</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -4036,7 +4353,7 @@
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>0.01</v>
       </c>
       <c r="C13" s="14" t="s">
@@ -4047,7 +4364,7 @@
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="14" t="s">
@@ -4058,7 +4375,7 @@
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>360.01</v>
       </c>
       <c r="C15" s="14" t="s">
@@ -4069,7 +4386,7 @@
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C16" s="14" t="s">
@@ -4083,10 +4400,10 @@
       <c r="B17" s="19">
         <v>1</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="30" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4094,18 +4411,18 @@
       <c r="B18" s="19">
         <v>180</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B19" s="21">
+      <c r="B19" s="20">
         <v>-180</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D19" s="14" t="s">
@@ -4113,10 +4430,10 @@
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="14" t="s">
@@ -4124,10 +4441,10 @@
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B21" s="21">
-        <v>0</v>
-      </c>
-      <c r="C21" s="22" t="s">
+      <c r="B21" s="20">
+        <v>0</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D21" s="14" t="s">
@@ -4135,10 +4452,10 @@
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B22" s="21">
+      <c r="B22" s="20">
         <v>0.01</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="14" t="s">
@@ -4146,10 +4463,10 @@
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="14" t="s">
@@ -4157,10 +4474,10 @@
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <v>360.01</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="14" t="s">
@@ -4168,10 +4485,10 @@
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="14" t="s">
@@ -4182,10 +4499,10 @@
       <c r="B26" s="19">
         <v>1</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="30" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4193,18 +4510,18 @@
       <c r="B27" s="19">
         <v>180</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="30" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B28" s="21">
+      <c r="B28" s="20">
         <v>-180</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D28" s="14" t="s">
@@ -4212,10 +4529,10 @@
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D29" s="14" t="s">
@@ -4223,10 +4540,10 @@
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B30" s="21">
-        <v>0</v>
-      </c>
-      <c r="C30" s="22" t="s">
+      <c r="B30" s="20">
+        <v>0</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D30" s="14" t="s">
@@ -4234,10 +4551,10 @@
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B31" s="21">
+      <c r="B31" s="20">
         <v>0.01</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D31" s="14" t="s">
@@ -4245,10 +4562,10 @@
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D32" s="14" t="s">
@@ -4256,10 +4573,10 @@
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B33" s="21">
+      <c r="B33" s="20">
         <v>360.01</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D33" s="14" t="s">
@@ -4267,10 +4584,10 @@
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D34" s="14" t="s">
@@ -4278,45 +4595,45 @@
       </c>
     </row>
     <row r="37" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="61" t="s">
+      <c r="B37" s="76" t="s">
         <v>198</v>
       </c>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B38" s="62" t="s">
+      <c r="B38" s="77" t="s">
         <v>190</v>
       </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="C40" s="64"/>
-      <c r="D40" s="65"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="75"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="D41" s="22" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="29" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4327,7 +4644,7 @@
       <c r="C43" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D43" s="31" t="s">
+      <c r="D43" s="30" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4338,12 +4655,12 @@
       <c r="C44" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D44" s="31" t="s">
+      <c r="D44" s="30" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B45" s="21">
+      <c r="B45" s="20">
         <v>-180</v>
       </c>
       <c r="C45" s="14" t="s">
@@ -4354,7 +4671,7 @@
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B46" s="22" t="s">
+      <c r="B46" s="21" t="s">
         <v>58</v>
       </c>
       <c r="C46" s="14" t="s">
@@ -4365,7 +4682,7 @@
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B47" s="21">
+      <c r="B47" s="20">
         <v>0</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -4376,7 +4693,7 @@
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B48" s="21">
+      <c r="B48" s="20">
         <v>0.01</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -4387,7 +4704,7 @@
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C49" s="14" t="s">
@@ -4398,7 +4715,7 @@
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B50" s="21">
+      <c r="B50" s="20">
         <v>360.01</v>
       </c>
       <c r="C50" s="14" t="s">
@@ -4409,7 +4726,7 @@
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C51" s="14" t="s">
@@ -4423,10 +4740,10 @@
       <c r="B52" s="19">
         <v>1</v>
       </c>
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D52" s="31" t="s">
+      <c r="D52" s="30" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4434,18 +4751,18 @@
       <c r="B53" s="19">
         <v>180</v>
       </c>
-      <c r="C53" s="22" t="s">
+      <c r="C53" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D53" s="31" t="s">
+      <c r="D53" s="30" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B54" s="21">
+      <c r="B54" s="20">
         <v>-180</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D54" s="14" t="s">
@@ -4453,10 +4770,10 @@
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C55" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D55" s="14" t="s">
@@ -4464,10 +4781,10 @@
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B56" s="21">
-        <v>0</v>
-      </c>
-      <c r="C56" s="22" t="s">
+      <c r="B56" s="20">
+        <v>0</v>
+      </c>
+      <c r="C56" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D56" s="14" t="s">
@@ -4475,10 +4792,10 @@
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B57" s="21">
+      <c r="B57" s="20">
         <v>0.01</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D57" s="14" t="s">
@@ -4486,10 +4803,10 @@
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B58" s="22" t="s">
+      <c r="B58" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="22" t="s">
+      <c r="C58" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D58" s="14" t="s">
@@ -4497,10 +4814,10 @@
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B59" s="21">
+      <c r="B59" s="20">
         <v>360.01</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="C59" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D59" s="14" t="s">
@@ -4508,10 +4825,10 @@
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B60" s="22" t="s">
+      <c r="B60" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="C60" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="14" t="s">
@@ -4522,10 +4839,10 @@
       <c r="B61" s="19">
         <v>1</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="C61" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D61" s="31" t="s">
+      <c r="D61" s="30" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4533,18 +4850,18 @@
       <c r="B62" s="19">
         <v>180</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D62" s="31" t="s">
+      <c r="D62" s="30" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B63" s="21">
+      <c r="B63" s="20">
         <v>-180</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D63" s="14" t="s">
@@ -4552,10 +4869,10 @@
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D64" s="14" t="s">
@@ -4563,10 +4880,10 @@
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B65" s="21">
-        <v>0</v>
-      </c>
-      <c r="C65" s="22" t="s">
+      <c r="B65" s="20">
+        <v>0</v>
+      </c>
+      <c r="C65" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D65" s="14" t="s">
@@ -4574,10 +4891,10 @@
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B66" s="21">
+      <c r="B66" s="20">
         <v>0.01</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="C66" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D66" s="14" t="s">
@@ -4585,10 +4902,10 @@
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C67" s="22" t="s">
+      <c r="C67" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D67" s="14" t="s">
@@ -4596,10 +4913,10 @@
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B68" s="21">
+      <c r="B68" s="20">
         <v>360.01</v>
       </c>
-      <c r="C68" s="22" t="s">
+      <c r="C68" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D68" s="14" t="s">
@@ -4607,10 +4924,10 @@
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B69" s="22" t="s">
+      <c r="B69" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C69" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D69" s="14" t="s">
@@ -4641,45 +4958,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="75"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="26" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5010,22 +5327,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -5112,45 +5429,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>262</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B5" s="74" t="s">
         <v>263</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
-        <v>264</v>
-      </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="75"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="26" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5161,7 +5478,7 @@
       <c r="C8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="39">
         <v>1</v>
       </c>
     </row>
@@ -5172,7 +5489,7 @@
       <c r="C9" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="39">
         <v>180</v>
       </c>
     </row>
@@ -5183,7 +5500,7 @@
       <c r="C10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="39">
         <v>-180</v>
       </c>
     </row>
@@ -5195,7 +5512,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.15">
@@ -5205,7 +5522,7 @@
       <c r="C12" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>0</v>
       </c>
     </row>
@@ -5216,7 +5533,7 @@
       <c r="C13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="36">
         <v>0.01</v>
       </c>
     </row>
@@ -5227,8 +5544,8 @@
       <c r="C14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="41" t="s">
-        <v>266</v>
+      <c r="D14" s="40" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.15">
@@ -5238,7 +5555,7 @@
       <c r="C15" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="39">
         <v>0</v>
       </c>
     </row>
@@ -5249,7 +5566,7 @@
       <c r="C16" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="39">
         <v>0</v>
       </c>
     </row>
@@ -5260,7 +5577,7 @@
       <c r="C17" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5271,7 +5588,7 @@
       <c r="C18" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5282,7 +5599,7 @@
       <c r="C19" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5293,7 +5610,7 @@
       <c r="C20" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5304,7 +5621,7 @@
       <c r="C21" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5315,7 +5632,7 @@
       <c r="C22" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5326,7 +5643,7 @@
       <c r="C23" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5337,7 +5654,7 @@
       <c r="C24" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5348,7 +5665,7 @@
       <c r="C25" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5359,7 +5676,7 @@
       <c r="C26" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D26" s="42">
+      <c r="D26" s="41">
         <v>-0.125</v>
       </c>
     </row>
@@ -5370,7 +5687,7 @@
       <c r="C27" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="41">
         <v>0</v>
       </c>
     </row>
@@ -5381,7 +5698,7 @@
       <c r="C28" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="41">
         <v>0</v>
       </c>
     </row>
@@ -5392,7 +5709,7 @@
       <c r="C29" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="41">
         <v>-0.125</v>
       </c>
     </row>
@@ -5403,7 +5720,7 @@
       <c r="C30" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="41">
         <v>0</v>
       </c>
     </row>
@@ -5414,7 +5731,7 @@
       <c r="C31" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="41">
         <v>0.01</v>
       </c>
     </row>
@@ -5425,8 +5742,8 @@
       <c r="C32" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D32" s="43" t="s">
-        <v>267</v>
+      <c r="D32" s="42" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.15">
@@ -5436,8 +5753,8 @@
       <c r="C33" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D33" s="43" t="s">
-        <v>268</v>
+      <c r="D33" s="42" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.15">
@@ -5447,8 +5764,8 @@
       <c r="C34" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="43" t="s">
-        <v>269</v>
+      <c r="D34" s="42" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -5472,45 +5789,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
     </row>
     <row r="3" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="75"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="26" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5812,45 +6129,45 @@
       </c>
     </row>
     <row r="38" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="76" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
     </row>
     <row r="39" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="77" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="65"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="75"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="26" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6174,18 +6491,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B3" s="55" t="s">
-        <v>288</v>
+      <c r="B3" s="44" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B9" s="55" t="s">
-        <v>313</v>
+      <c r="B9" s="44" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.15">
@@ -6215,22 +6532,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>252</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -6252,16 +6569,16 @@
       <c r="B8" s="8">
         <v>1</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="34"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B9" s="8">
         <v>180</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -6269,16 +6586,16 @@
       <c r="B10" s="8">
         <v>-180</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="27" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="16"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B11" s="37">
+      <c r="B11" s="36">
         <v>361</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -6292,19 +6609,19 @@
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B13" s="37">
+      <c r="B13" s="36">
         <v>0.47942553860420301</v>
       </c>
       <c r="C13" s="7">
         <v>0.5</v>
       </c>
-      <c r="D13" s="32"/>
+      <c r="D13" s="31"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -6312,35 +6629,35 @@
       <c r="B15" s="8">
         <v>360.01</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>-360.01</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="76" t="s">
         <v>255</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="76"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="77" t="s">
         <v>256</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="77"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>257</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="75"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -6357,22 +6674,22 @@
       <c r="C25" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E25" s="33"/>
+      <c r="E25" s="32"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B26" s="8">
         <v>1</v>
       </c>
-      <c r="C26" s="34">
-        <v>0</v>
-      </c>
-      <c r="E26" s="35"/>
+      <c r="C26" s="33">
+        <v>0</v>
+      </c>
+      <c r="E26" s="34"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
         <v>180</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -6380,16 +6697,16 @@
       <c r="B28" s="8">
         <v>-180</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="36"/>
+      <c r="E28" s="35"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B29" s="37">
+      <c r="B29" s="36">
         <v>361</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -6397,12 +6714,12 @@
       <c r="B30" s="8">
         <v>0</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" s="33" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B31" s="37">
+      <c r="B31" s="36">
         <v>0.47942553860420301</v>
       </c>
       <c r="C31" s="14" t="s">
@@ -6410,10 +6727,10 @@
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -6421,35 +6738,35 @@
       <c r="B33" s="8">
         <v>360.01</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>-360.01</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="76" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="61"/>
+      <c r="C38" s="76"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="77" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="62"/>
+      <c r="C39" s="77"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="74" t="s">
         <v>243</v>
       </c>
-      <c r="C41" s="65"/>
+      <c r="C41" s="75"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B42" s="4" t="s">
@@ -6540,45 +6857,45 @@
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B56" s="61" t="s">
+      <c r="B56" s="76" t="s">
         <v>218</v>
       </c>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
+      <c r="C56" s="76"/>
+      <c r="D56" s="76"/>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B57" s="62" t="s">
+      <c r="B57" s="77" t="s">
         <v>219</v>
       </c>
-      <c r="C57" s="62"/>
-      <c r="D57" s="62"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="77"/>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B59" s="63" t="s">
+      <c r="B59" s="74" t="s">
         <v>217</v>
       </c>
-      <c r="C59" s="64"/>
-      <c r="D59" s="65"/>
+      <c r="C59" s="78"/>
+      <c r="D59" s="75"/>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B60" s="26" t="s">
+      <c r="B60" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="C60" s="26" t="s">
+      <c r="C60" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="26" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B61" s="24" t="s">
+      <c r="B61" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="C61" s="24" t="s">
+      <c r="C61" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="D61" s="24" t="s">
+      <c r="D61" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6909,22 +7226,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -7018,22 +7335,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="76"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="77"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="75"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -7127,22 +7444,22 @@
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="61"/>
+      <c r="C38" s="76"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="62"/>
+      <c r="C39" s="77"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="65"/>
+      <c r="C41" s="75"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B42" s="4" t="s">
@@ -7259,22 +7576,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -7317,7 +7634,7 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <v>361</v>
       </c>
       <c r="C11" s="6">
@@ -7341,7 +7658,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C14" s="6">
@@ -7357,7 +7674,7 @@
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>-360.01</v>
       </c>
       <c r="C16" s="6">
@@ -7365,22 +7682,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="76"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="77"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="75"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -7423,7 +7740,7 @@
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>361</v>
       </c>
       <c r="C29" s="6">
@@ -7447,7 +7764,7 @@
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C32" s="6">
@@ -7463,7 +7780,7 @@
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>-360.01</v>
       </c>
       <c r="C34" s="6">
@@ -7494,22 +7811,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -7577,10 +7894,10 @@
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B14" s="14" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.15">
@@ -7600,22 +7917,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="76" t="s">
         <v>172</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="76"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="77" t="s">
         <v>173</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="77"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="75"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -7684,10 +8001,10 @@
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B32" s="14" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.15">
@@ -7730,22 +8047,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -7764,7 +8081,7 @@
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <v>1</v>
       </c>
       <c r="C8" s="14" t="s">
@@ -7772,7 +8089,7 @@
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B9" s="21">
+      <c r="B9" s="20">
         <v>180</v>
       </c>
       <c r="C9" s="14" t="s">
@@ -7780,7 +8097,7 @@
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <v>-180</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -7788,7 +8105,7 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>58</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -7796,7 +8113,7 @@
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <v>0</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -7804,7 +8121,7 @@
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>0.01</v>
       </c>
       <c r="C13" s="14" t="s">
@@ -7812,7 +8129,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="14" t="s">
@@ -7820,7 +8137,7 @@
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>360.01</v>
       </c>
       <c r="C15" s="14" t="s">
@@ -7828,7 +8145,7 @@
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C16" s="14" t="s">
@@ -7836,22 +8153,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="76"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="77"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="75"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -7870,7 +8187,7 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B26" s="21">
+      <c r="B26" s="20">
         <v>1</v>
       </c>
       <c r="C26" s="14" t="s">
@@ -7878,7 +8195,7 @@
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <v>180</v>
       </c>
       <c r="C27" s="14" t="s">
@@ -7886,7 +8203,7 @@
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B28" s="21">
+      <c r="B28" s="20">
         <v>-180</v>
       </c>
       <c r="C28" s="14" t="s">
@@ -7894,7 +8211,7 @@
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="21" t="s">
         <v>58</v>
       </c>
       <c r="C29" s="14" t="s">
@@ -7902,7 +8219,7 @@
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B30" s="21">
+      <c r="B30" s="20">
         <v>0</v>
       </c>
       <c r="C30" s="14" t="s">
@@ -7910,7 +8227,7 @@
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B31" s="21">
+      <c r="B31" s="20">
         <v>0.01</v>
       </c>
       <c r="C31" s="14" t="s">
@@ -7918,7 +8235,7 @@
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="14" t="s">
@@ -7926,7 +8243,7 @@
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B33" s="21">
+      <c r="B33" s="20">
         <v>360.01</v>
       </c>
       <c r="C33" s="14" t="s">
@@ -7934,7 +8251,7 @@
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C34" s="14" t="s">
@@ -7942,28 +8259,28 @@
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="61"/>
+      <c r="C38" s="76"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="62"/>
+      <c r="C39" s="77"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="65"/>
+      <c r="C41" s="75"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B42" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="22" t="s">
         <v>0</v>
       </c>
     </row>
@@ -7971,12 +8288,12 @@
       <c r="B43" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B44" s="21">
+      <c r="B44" s="20">
         <v>1</v>
       </c>
       <c r="C44" s="14" t="s">
@@ -7984,7 +8301,7 @@
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B45" s="21">
+      <c r="B45" s="20">
         <v>180</v>
       </c>
       <c r="C45" s="14" t="s">
@@ -7992,7 +8309,7 @@
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B46" s="21">
+      <c r="B46" s="20">
         <v>-180</v>
       </c>
       <c r="C46" s="14" t="s">
@@ -8000,7 +8317,7 @@
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="21" t="s">
         <v>58</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -8008,7 +8325,7 @@
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B48" s="21">
+      <c r="B48" s="20">
         <v>0</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -8016,7 +8333,7 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B49" s="21">
+      <c r="B49" s="20">
         <v>0.01</v>
       </c>
       <c r="C49" s="14" t="s">
@@ -8024,7 +8341,7 @@
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B50" s="22" t="s">
+      <c r="B50" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C50" s="14" t="s">
@@ -8074,22 +8391,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="65"/>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -8132,7 +8449,7 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <v>361</v>
       </c>
       <c r="C11" s="7">
@@ -8156,7 +8473,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C14" s="7">
@@ -8172,7 +8489,7 @@
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>-360.01</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -8180,22 +8497,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="76"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="77" t="s">
         <v>208</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="77"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>209</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="75"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -8238,7 +8555,7 @@
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>361</v>
       </c>
       <c r="C29" s="19" t="s">
@@ -8262,7 +8579,7 @@
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C32" s="14" t="s">
@@ -8278,7 +8595,7 @@
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>-360.01</v>
       </c>
       <c r="C34" s="14" t="s">
@@ -8286,45 +8603,45 @@
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="76" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="77" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="65"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="75"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="26" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -8362,7 +8679,7 @@
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B47" s="28">
+      <c r="B47" s="27">
         <v>361</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -8395,7 +8712,7 @@
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B50" s="28">
+      <c r="B50" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C50" s="14" t="s">
@@ -8417,7 +8734,7 @@
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B52" s="28">
+      <c r="B52" s="27">
         <v>-360.01</v>
       </c>
       <c r="C52" s="14" t="s">
@@ -8461,7 +8778,7 @@
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B56" s="28">
+      <c r="B56" s="27">
         <v>361</v>
       </c>
       <c r="C56" s="14" t="s">
@@ -8494,7 +8811,7 @@
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B59" s="28">
+      <c r="B59" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C59" s="14" t="s">
@@ -8516,7 +8833,7 @@
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B61" s="28">
+      <c r="B61" s="27">
         <v>-360.01</v>
       </c>
       <c r="C61" s="14" t="s">
@@ -8560,7 +8877,7 @@
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B65" s="28">
+      <c r="B65" s="27">
         <v>361</v>
       </c>
       <c r="C65" s="14" t="s">
@@ -8593,7 +8910,7 @@
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B68" s="28">
+      <c r="B68" s="27">
         <v>360.98977874384701</v>
       </c>
       <c r="C68" s="14" t="s">
@@ -8615,13 +8932,13 @@
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B70" s="28">
+      <c r="B70" s="27">
         <v>-360.01</v>
       </c>
       <c r="C70" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="D70" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8643,789 +8960,839 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B2:E101"/>
+  <dimension ref="B2:F99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="26.5" customWidth="1"/>
-    <col min="4" max="5" width="18.33203125" customWidth="1"/>
+    <col min="2" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
+    <row r="2" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B2" s="79" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2" s="79"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B3" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="C2" s="61"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
+      <c r="C3" s="80"/>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B5" s="81" t="s">
         <v>271</v>
       </c>
-      <c r="C3" s="62"/>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
+      <c r="C5" s="82"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B6" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B7" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B8" s="60">
+        <v>1</v>
+      </c>
+      <c r="C8" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B9" s="61">
+        <v>180</v>
+      </c>
+      <c r="C9" s="61">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B10" s="60">
+        <v>-180</v>
+      </c>
+      <c r="C10" s="60">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B11" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B12" s="60">
+        <v>0</v>
+      </c>
+      <c r="C12" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B13" s="61">
+        <v>0.01</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B14" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B15" s="61">
+        <v>360.01</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B16" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B20" s="79" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="79"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B21" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="80"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B23" s="81" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" s="82"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B24" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="59" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B25" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B26" s="60">
+        <v>1</v>
+      </c>
+      <c r="C26" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B27" s="61">
+        <v>180</v>
+      </c>
+      <c r="C27" s="50">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B28" s="60">
+        <v>-180</v>
+      </c>
+      <c r="C28" s="49">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B29" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="50">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B30" s="60">
+        <v>0</v>
+      </c>
+      <c r="C30" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B31" s="61">
+        <v>0.01</v>
+      </c>
+      <c r="C31" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B32" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="49">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B33" s="61">
+        <v>360.01</v>
+      </c>
+      <c r="C33" s="50">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B34" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="49">
+        <v>-361</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B38" s="79" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="79"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B39" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="80"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B41" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="82"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B42" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="59" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B43" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B44" s="60">
+        <v>1</v>
+      </c>
+      <c r="C44" s="56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B45" s="61">
+        <v>180</v>
+      </c>
+      <c r="C45" s="54" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B46" s="60">
+        <v>-180</v>
+      </c>
+      <c r="C46" s="56" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B47" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B48" s="60">
+        <v>0</v>
+      </c>
+      <c r="C48" s="56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B49" s="61">
+        <v>0.01</v>
+      </c>
+      <c r="C49" s="54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B50" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="56" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B51" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B52" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" ht="14" x14ac:dyDescent="0.15">
+      <c r="B56" s="79" t="s">
+        <v>203</v>
+      </c>
+      <c r="C56" s="79"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B57" s="80" t="s">
+        <v>204</v>
+      </c>
+      <c r="C57" s="80"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B59" s="81" t="s">
+        <v>205</v>
+      </c>
+      <c r="C59" s="82"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B60" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="59" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B61" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B62" s="60">
+        <v>1</v>
+      </c>
+      <c r="C62" s="56" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B63" s="61">
+        <v>180</v>
+      </c>
+      <c r="C63" s="54" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B64" s="60">
+        <v>-180</v>
+      </c>
+      <c r="C64" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B65" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65" s="54" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B66" s="60">
+        <v>0</v>
+      </c>
+      <c r="C66" s="56" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B67" s="61">
+        <v>0.01</v>
+      </c>
+      <c r="C67" s="54" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B68" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" s="56" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B69" s="61">
+        <v>360.01</v>
+      </c>
+      <c r="C69" s="54" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B70" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" s="56" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B74" s="70" t="s">
+        <v>273</v>
+      </c>
+      <c r="C74" s="71"/>
+      <c r="D74" s="71"/>
+      <c r="E74" s="71"/>
+      <c r="F74" s="71"/>
+    </row>
+    <row r="75" spans="2:6" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B75" s="83" t="s">
+        <v>274</v>
+      </c>
+      <c r="C75" s="84"/>
+      <c r="D75" s="84"/>
+      <c r="E75" s="84"/>
+      <c r="F75" s="84"/>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B77" s="85" t="s">
         <v>272</v>
       </c>
-      <c r="C5" s="65"/>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B6" s="4" t="s">
+      <c r="C77" s="86"/>
+      <c r="D77" s="86"/>
+      <c r="E77" s="86"/>
+      <c r="F77" s="87"/>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B78" s="59" t="s">
+        <v>316</v>
+      </c>
+      <c r="C78" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B7" s="17" t="s">
+      <c r="D78" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="E78" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F78" s="59" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B79" s="59" t="s">
+        <v>316</v>
+      </c>
+      <c r="C79" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B8" s="19">
-        <v>1</v>
-      </c>
-      <c r="C8" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B9" s="19">
+      <c r="D79" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="E79" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F79" s="58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B80" s="49">
+        <v>1</v>
+      </c>
+      <c r="C80" s="53">
+        <v>1</v>
+      </c>
+      <c r="D80" s="52">
+        <v>2</v>
+      </c>
+      <c r="E80" s="52">
+        <v>1</v>
+      </c>
+      <c r="F80" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="50">
+        <v>2</v>
+      </c>
+      <c r="C81" s="57">
         <v>180</v>
       </c>
-      <c r="C9" s="19">
+      <c r="D81" s="51">
+        <v>2</v>
+      </c>
+      <c r="E81" s="51">
+        <v>1</v>
+      </c>
+      <c r="F81" s="57">
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B10" s="19">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B82" s="49">
+        <v>3</v>
+      </c>
+      <c r="C82" s="53">
         <v>-180</v>
       </c>
-      <c r="C10" s="19">
+      <c r="D82" s="52">
+        <v>2</v>
+      </c>
+      <c r="E82" s="52">
+        <v>1</v>
+      </c>
+      <c r="F82" s="53">
         <v>-180</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B11" s="14" t="s">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B83" s="50">
+        <v>4</v>
+      </c>
+      <c r="C83" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B12" s="19">
-        <v>0</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B13" s="19">
+      <c r="D83" s="51">
+        <v>2</v>
+      </c>
+      <c r="E83" s="51">
+        <v>1</v>
+      </c>
+      <c r="F83" s="51">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B84" s="49">
+        <v>5</v>
+      </c>
+      <c r="C84" s="53">
+        <v>0</v>
+      </c>
+      <c r="D84" s="52">
+        <v>2</v>
+      </c>
+      <c r="E84" s="52">
+        <v>1</v>
+      </c>
+      <c r="F84" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B85" s="50">
+        <v>6</v>
+      </c>
+      <c r="C85" s="57">
         <v>0.01</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B14" s="14" t="s">
+      <c r="D85" s="51">
+        <v>2</v>
+      </c>
+      <c r="E85" s="51">
+        <v>1</v>
+      </c>
+      <c r="F85" s="62">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B86" s="49">
+        <v>7</v>
+      </c>
+      <c r="C86" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B15" s="19">
+      <c r="D86" s="52">
+        <v>2</v>
+      </c>
+      <c r="E86" s="52">
+        <v>1</v>
+      </c>
+      <c r="F86" s="52">
+        <v>360.98</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B87" s="50">
+        <v>8</v>
+      </c>
+      <c r="C87" s="57">
         <v>360.01</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B16" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" s="61"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
-        <v>170</v>
-      </c>
-      <c r="C21" s="62"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="C23" s="65"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B24" s="4" t="s">
+      <c r="D87" s="51">
+        <v>2</v>
+      </c>
+      <c r="E87" s="51">
+        <v>1</v>
+      </c>
+      <c r="F87" s="51">
+        <v>360.01</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B88" s="49">
+        <v>9</v>
+      </c>
+      <c r="C88" s="52">
+        <v>-360.01</v>
+      </c>
+      <c r="D88" s="52">
+        <v>2</v>
+      </c>
+      <c r="E88" s="52">
+        <v>1</v>
+      </c>
+      <c r="F88" s="52">
+        <v>-360.01</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B89" s="50">
+        <v>10</v>
+      </c>
+      <c r="C89" s="50">
+        <v>1</v>
+      </c>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B90" s="49">
+        <v>11</v>
+      </c>
+      <c r="C90" s="49">
+        <v>1</v>
+      </c>
+      <c r="D90" s="49"/>
+      <c r="E90" s="49">
+        <v>1</v>
+      </c>
+      <c r="F90" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B91" s="50">
+        <v>12</v>
+      </c>
+      <c r="C91" s="50">
+        <v>1</v>
+      </c>
+      <c r="D91" s="50">
+        <v>1</v>
+      </c>
+      <c r="E91" s="50"/>
+      <c r="F91" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B92" s="49">
+        <v>13</v>
+      </c>
+      <c r="C92" s="49">
+        <v>0</v>
+      </c>
+      <c r="D92" s="49">
+        <v>0</v>
+      </c>
+      <c r="E92" s="49">
+        <v>0</v>
+      </c>
+      <c r="F92" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B93" s="50">
+        <v>14</v>
+      </c>
+      <c r="C93" s="63">
+        <v>32.456785431267001</v>
+      </c>
+      <c r="D93" s="51">
+        <v>2</v>
+      </c>
+      <c r="E93" s="51">
+        <v>0</v>
+      </c>
+      <c r="F93" s="50">
+        <v>32.46</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B94" s="49">
+        <v>15</v>
+      </c>
+      <c r="C94" s="49">
+        <v>32.284999999999997</v>
+      </c>
+      <c r="D94" s="52">
+        <v>2</v>
+      </c>
+      <c r="E94" s="52">
+        <v>1</v>
+      </c>
+      <c r="F94" s="49">
+        <v>32.28</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B95" s="50">
+        <v>16</v>
+      </c>
+      <c r="C95" s="63">
+        <v>32.456785431267001</v>
+      </c>
+      <c r="D95" s="51">
+        <v>2</v>
+      </c>
+      <c r="E95" s="51">
+        <v>2</v>
+      </c>
+      <c r="F95" s="50">
+        <v>32.46</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B96" s="49">
+        <v>17</v>
+      </c>
+      <c r="C96" s="64">
+        <v>32.456785431267001</v>
+      </c>
+      <c r="D96" s="52">
+        <v>2</v>
+      </c>
+      <c r="E96" s="52">
+        <v>3</v>
+      </c>
+      <c r="F96" s="49">
+        <v>32.450000000000003</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="50">
+        <v>18</v>
+      </c>
+      <c r="C97" s="63">
+        <v>32.456785431267001</v>
+      </c>
+      <c r="D97" s="51">
+        <v>2</v>
+      </c>
+      <c r="E97" s="51">
+        <v>4</v>
+      </c>
+      <c r="F97" s="50">
+        <v>32.46</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B98" s="49">
+        <v>19</v>
+      </c>
+      <c r="C98" s="64">
+        <v>32.456785431267001</v>
+      </c>
+      <c r="D98" s="52">
+        <v>2</v>
+      </c>
+      <c r="E98" s="52">
         <v>5</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B25" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B26" s="19">
-        <v>1</v>
-      </c>
-      <c r="C26" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B27" s="19">
-        <v>180</v>
-      </c>
-      <c r="C27" s="6">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B28" s="19">
-        <v>-180</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-180</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B29" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="6">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B30" s="19">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B31" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B32" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="6">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B33" s="19">
-        <v>360.01</v>
-      </c>
-      <c r="C33" s="6">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B34" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-361</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="61"/>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="62" t="s">
-        <v>108</v>
-      </c>
-      <c r="C39" s="62"/>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="63" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" s="65"/>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B42" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B43" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B44" s="19">
-        <v>1</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B45" s="19">
-        <v>180</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B46" s="19">
-        <v>-180</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B47" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B48" s="19">
-        <v>0</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B49" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B50" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B51" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B52" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B56" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="C56" s="61"/>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B57" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="C57" s="62"/>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B59" s="63" t="s">
-        <v>205</v>
-      </c>
-      <c r="C59" s="65"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B60" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B61" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B62" s="19">
-        <v>1</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B63" s="19">
-        <v>180</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B64" s="19">
-        <v>-180</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B65" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B66" s="19">
-        <v>0</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B67" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B68" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B69" s="19">
-        <v>360.01</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B70" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B74" s="61" t="s">
-        <v>274</v>
-      </c>
-      <c r="C74" s="61"/>
-      <c r="D74" s="61"/>
-      <c r="E74" s="61"/>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B75" s="62" t="s">
-        <v>275</v>
-      </c>
-      <c r="C75" s="62"/>
-      <c r="D75" s="62"/>
-      <c r="E75" s="62"/>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B77" s="63" t="s">
-        <v>273</v>
-      </c>
-      <c r="C77" s="64"/>
-      <c r="D77" s="64"/>
-      <c r="E77" s="65"/>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B78" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="D78" s="25" t="s">
-        <v>277</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B79" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="D79" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="E79" s="18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B80" s="8">
-        <v>1</v>
-      </c>
-      <c r="C80" s="28">
+      <c r="F98" s="49">
+        <v>32.46</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B99" s="50">
+        <v>20</v>
+      </c>
+      <c r="C99" s="63">
+        <v>32.456785431267001</v>
+      </c>
+      <c r="D99" s="51">
         <v>2</v>
       </c>
-      <c r="D80" s="28">
-        <v>1</v>
-      </c>
-      <c r="E80" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B81" s="8">
-        <v>180</v>
-      </c>
-      <c r="C81" s="28">
-        <v>2</v>
-      </c>
-      <c r="D81" s="28">
-        <v>1</v>
-      </c>
-      <c r="E81" s="8">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B82" s="8">
-        <v>-180</v>
-      </c>
-      <c r="C82" s="28">
-        <v>2</v>
-      </c>
-      <c r="D82" s="28">
-        <v>1</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-180</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B83" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="C83" s="28">
-        <v>2</v>
-      </c>
-      <c r="D83" s="28">
-        <v>1</v>
-      </c>
-      <c r="E83" s="28">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B84" s="8">
-        <v>0</v>
-      </c>
-      <c r="C84" s="28">
-        <v>2</v>
-      </c>
-      <c r="D84" s="28">
-        <v>1</v>
-      </c>
-      <c r="E84" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B85" s="8">
-        <v>0.01</v>
-      </c>
-      <c r="C85" s="28">
-        <v>2</v>
-      </c>
-      <c r="D85" s="28">
-        <v>1</v>
-      </c>
-      <c r="E85" s="37">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B86" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C86" s="28">
-        <v>2</v>
-      </c>
-      <c r="D86" s="28">
-        <v>1</v>
-      </c>
-      <c r="E86" s="28">
-        <v>360.98</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B87" s="8">
-        <v>360.01</v>
-      </c>
-      <c r="C87" s="28">
-        <v>2</v>
-      </c>
-      <c r="D87" s="28">
-        <v>1</v>
-      </c>
-      <c r="E87" s="28">
-        <v>360.01</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B88" s="28">
-        <v>-360.01</v>
-      </c>
-      <c r="C88" s="28">
-        <v>2</v>
-      </c>
-      <c r="D88" s="28">
-        <v>1</v>
-      </c>
-      <c r="E88" s="28">
-        <v>-360.01</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B89" s="6">
-        <v>1</v>
-      </c>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B90" s="6">
-        <v>1</v>
-      </c>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6">
-        <v>1</v>
-      </c>
-      <c r="E90" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B91" s="6">
-        <v>1</v>
-      </c>
-      <c r="C91" s="6">
-        <v>1</v>
-      </c>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B92" s="6">
-        <v>0</v>
-      </c>
-      <c r="C92" s="6">
-        <v>0</v>
-      </c>
-      <c r="D92" s="6">
-        <v>0</v>
-      </c>
-      <c r="E92" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B93" s="46">
-        <v>32.456785431267001</v>
-      </c>
-      <c r="C93" s="44">
-        <v>2</v>
-      </c>
-      <c r="D93" s="44">
-        <v>0</v>
-      </c>
-      <c r="E93" s="45">
+      <c r="E99" s="51">
+        <v>6</v>
+      </c>
+      <c r="F99" s="50">
         <v>32.46</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B94" s="6">
-        <v>32.284999999999997</v>
-      </c>
-      <c r="C94" s="28">
-        <v>2</v>
-      </c>
-      <c r="D94" s="28">
-        <v>1</v>
-      </c>
-      <c r="E94" s="6">
-        <v>32.28</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B95" s="47">
-        <v>32.456785431267001</v>
-      </c>
-      <c r="C95" s="28">
-        <v>2</v>
-      </c>
-      <c r="D95" s="28">
-        <v>2</v>
-      </c>
-      <c r="E95" s="6">
-        <v>32.46</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B96" s="47">
-        <v>32.456785431267001</v>
-      </c>
-      <c r="C96" s="28">
-        <v>2</v>
-      </c>
-      <c r="D96" s="28">
-        <v>3</v>
-      </c>
-      <c r="E96" s="6">
-        <v>32.450000000000003</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B97" s="47">
-        <v>32.456785431267001</v>
-      </c>
-      <c r="C97" s="28">
-        <v>2</v>
-      </c>
-      <c r="D97" s="28">
-        <v>4</v>
-      </c>
-      <c r="E97" s="6">
-        <v>32.46</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B98" s="47">
-        <v>32.456785431267001</v>
-      </c>
-      <c r="C98" s="28">
-        <v>2</v>
-      </c>
-      <c r="D98" s="28">
-        <v>5</v>
-      </c>
-      <c r="E98" s="6">
-        <v>32.46</v>
-      </c>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B99" s="47">
-        <v>32.456785431267001</v>
-      </c>
-      <c r="C99" s="28">
-        <v>2</v>
-      </c>
-      <c r="D99" s="28">
-        <v>6</v>
-      </c>
-      <c r="E99" s="6">
-        <v>32.46</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B100" s="47"/>
-      <c r="C100" s="28"/>
-      <c r="D100" s="28"/>
-      <c r="E100" s="6"/>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B101" s="48">
-        <v>32.456785431267001</v>
-      </c>
-      <c r="C101" s="49">
-        <v>2</v>
-      </c>
-      <c r="D101" s="49">
-        <v>7</v>
-      </c>
-      <c r="E101" s="20">
-        <v>32.450000000000003</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B77:F77"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
@@ -9438,6 +9805,7 @@
     <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -9453,22 +9821,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="61" t="s">
-        <v>315</v>
-      </c>
-      <c r="C2" s="61"/>
+      <c r="B2" s="76" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="62" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="62"/>
+      <c r="B3" s="77" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="77"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="63" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" s="65"/>
+      <c r="B5" s="74" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" s="75"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -9559,32 +9927,32 @@
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B20" s="61" t="s">
-        <v>316</v>
-      </c>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
+      <c r="B20" s="76" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B21" s="62" t="s">
-        <v>289</v>
-      </c>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
+      <c r="B21" s="77" t="s">
+        <v>287</v>
+      </c>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="74" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="65"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="75"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="25" t="s">
-        <v>292</v>
+      <c r="C24" s="24" t="s">
+        <v>290</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>0</v>
@@ -9594,8 +9962,8 @@
       <c r="B25" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="29" t="s">
-        <v>292</v>
+      <c r="C25" s="28" t="s">
+        <v>290</v>
       </c>
       <c r="D25" s="18" t="s">
         <v>1</v>
@@ -9705,10 +10073,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.15">
@@ -9716,10 +10084,10 @@
         <v>180</v>
       </c>
       <c r="C36" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="D36" s="14" t="s">
         <v>293</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.15">
@@ -9727,10 +10095,10 @@
         <v>-180</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.15">
@@ -9738,10 +10106,10 @@
         <v>58</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.15">
@@ -9749,10 +10117,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.15">
@@ -9760,10 +10128,10 @@
         <v>0.01</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.15">
@@ -9771,10 +10139,10 @@
         <v>34</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.15">
@@ -9782,10 +10150,10 @@
         <v>360.01</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.15">
@@ -9793,10 +10161,10 @@
         <v>47</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.15">
@@ -9804,10 +10172,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.15">
@@ -9815,10 +10183,10 @@
         <v>180</v>
       </c>
       <c r="C45" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>303</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.15">
@@ -9826,10 +10194,10 @@
         <v>-180</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.15">
@@ -9837,10 +10205,10 @@
         <v>58</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.15">
@@ -9848,10 +10216,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.15">
@@ -9859,32 +10227,32 @@
         <v>0.01</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B50" s="54" t="s">
+      <c r="B50" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="C50" s="54" t="s">
-        <v>311</v>
-      </c>
-      <c r="D50" s="54" t="s">
-        <v>312</v>
+      <c r="C50" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="D50" s="43" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B51" s="54" t="s">
+      <c r="B51" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="54" t="s">
-        <v>303</v>
-      </c>
-      <c r="D51" s="54" t="s">
-        <v>307</v>
+      <c r="C51" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="D51" s="43" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.15">
@@ -9892,10 +10260,10 @@
         <v>360.01</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.15">
@@ -9903,10 +10271,10 @@
         <v>47</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/DEV/org.openl.rules.test/test-resources/functionality/Math.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/Math.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vpikus/Sources/OpenL/openl-tablets/DEV/org.openl.rules.test/test-resources/functionality/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C900D3-D862-3B4A-B111-F9CC5C08B033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4862A5FF-7075-6044-84E6-F3CB071E196C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34980" windowHeight="22600" tabRatio="765" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34980" windowHeight="22600" tabRatio="765" firstSheet="5" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="X" sheetId="5" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="IEEEremainder" sheetId="37" r:id="rId16"/>
     <sheet name="nextAfter" sheetId="22" r:id="rId17"/>
     <sheet name="random" sheetId="44" r:id="rId18"/>
+    <sheet name="floorDiv" sheetId="46" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -553,7 +554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="359">
   <si>
     <t>_res_</t>
   </si>
@@ -1516,6 +1517,120 @@
   </si>
   <si>
     <t>-7.010221256152988</t>
+  </si>
+  <si>
+    <t>dividend</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>return floorDiv(dividend, divisor);</t>
+  </si>
+  <si>
+    <t>Test floorDivMethodByte floorDivByteTest</t>
+  </si>
+  <si>
+    <t>Test floorDivMethodShort floorDivShortTest</t>
+  </si>
+  <si>
+    <t>Method Integer floorDivMethodInteger (Integer dividend, Integer divisor)</t>
+  </si>
+  <si>
+    <t>Test floorDivMethodInteger floorDivIntegerTest</t>
+  </si>
+  <si>
+    <t>Method Long floorDivMethodLong (Long dividend, Long divisor)</t>
+  </si>
+  <si>
+    <t>Test floorDivMethodLong floorDivLongTest</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>-3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>9223372036854775807</t>
+  </si>
+  <si>
+    <t>4611686018427387903</t>
+  </si>
+  <si>
+    <t>-9223372036854775808</t>
+  </si>
+  <si>
+    <t>-4611686018427387904</t>
+  </si>
+  <si>
+    <t>-9223372036854775807</t>
+  </si>
+  <si>
+    <t>Method Integer floorDivMethodByte (Byte dividend, Byte divisor)</t>
+  </si>
+  <si>
+    <t>Method Integer floorDivMethodShort (Short dividend, Short divisor)</t>
+  </si>
+  <si>
+    <t>Test floorDivMethodFloat floorDivFloatTest</t>
+  </si>
+  <si>
+    <t>Method Double floorDivMethodFloat (Float dividend, Float divisor)</t>
+  </si>
+  <si>
+    <t>Method Double floorDivMethodDouble (Double dividend, Double divisor)</t>
+  </si>
+  <si>
+    <t>Test floorDivMethodDouble floorDivDoubleTest</t>
+  </si>
+  <si>
+    <t>Method BigDecimal floorDivMethodBigDecimal (BigDecimal dividend, BigDecimal divisor)</t>
+  </si>
+  <si>
+    <t>Test floorDivMethodBigDecimal floorDivBigDecimalTest</t>
+  </si>
+  <si>
+    <t>Method BigInteger floorDivMethodBigInteger (BigInteger dividend, BigInteger divisor)</t>
+  </si>
+  <si>
+    <t>Test floorDivMethodBigInteger floorDivBigIntegerTest</t>
+  </si>
+  <si>
+    <t>-3.22</t>
+  </si>
+  <si>
+    <t>-1.75</t>
+  </si>
+  <si>
+    <t>3.22</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>203000745502000030060144252100</t>
+  </si>
+  <si>
+    <t>-203000745502000030060144252100</t>
+  </si>
+  <si>
+    <t>2092791190742268351135507753</t>
+  </si>
+  <si>
+    <t>-2092791190742268351135507754</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1647,7 @@
     <numFmt numFmtId="170" formatCode="0.000000000000"/>
     <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1677,6 +1792,18 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2020,7 +2147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2097,11 +2224,28 @@
     <xf numFmtId="0" fontId="20" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="21" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="21" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2114,6 +2258,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2599,22 +2749,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -2705,22 +2855,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="76"/>
+      <c r="C20" s="89"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="77"/>
+      <c r="C21" s="90"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="88"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -2819,22 +2969,22 @@
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="76" t="s">
+      <c r="B39" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="76"/>
+      <c r="C39" s="89"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B40" s="77" t="s">
+      <c r="B40" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="77"/>
+      <c r="C40" s="90"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B42" s="74" t="s">
+      <c r="B42" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="75"/>
+      <c r="C42" s="88"/>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B43" s="4" t="s">
@@ -2953,28 +3103,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="81" t="s">
         <v>282</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
     </row>
     <row r="3" spans="2:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="83" t="s">
         <v>283</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="85" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B6" s="47" t="s">
@@ -3181,28 +3331,28 @@
       <c r="E21" s="50"/>
     </row>
     <row r="25" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="82"/>
     </row>
     <row r="26" spans="2:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="72" t="s">
+      <c r="B26" s="83" t="s">
         <v>280</v>
       </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B28" s="68" t="s">
+      <c r="B28" s="85" t="s">
         <v>277</v>
       </c>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B29" s="47" t="s">
@@ -3434,22 +3584,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -3540,25 +3690,25 @@
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="90"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>160</v>
       </c>
-      <c r="C23" s="78"/>
-      <c r="D23" s="75"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="88"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -3904,22 +4054,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>260</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>261</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -4013,22 +4163,22 @@
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="76"/>
+      <c r="C20" s="89"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="77"/>
+      <c r="C21" s="90"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="88"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -4122,22 +4272,22 @@
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B37" s="76" t="s">
+      <c r="B37" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="76"/>
+      <c r="C37" s="89"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="77" t="s">
+      <c r="B38" s="90" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="77"/>
+      <c r="C38" s="90"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B40" s="74" t="s">
+      <c r="B40" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="75"/>
+      <c r="C40" s="88"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
@@ -4255,25 +4405,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="75"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="88"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B6" s="25" t="s">
@@ -4595,25 +4745,25 @@
       </c>
     </row>
     <row r="37" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="76" t="s">
+      <c r="B37" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="C37" s="76"/>
-      <c r="D37" s="76"/>
+      <c r="C37" s="89"/>
+      <c r="D37" s="89"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B38" s="77" t="s">
+      <c r="B38" s="90" t="s">
         <v>190</v>
       </c>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="90"/>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B40" s="74" t="s">
+      <c r="B40" s="87" t="s">
         <v>188</v>
       </c>
-      <c r="C40" s="78"/>
-      <c r="D40" s="75"/>
+      <c r="C40" s="91"/>
+      <c r="D40" s="88"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B41" s="25" t="s">
@@ -4958,25 +5108,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="75"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="88"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B6" s="25" t="s">
@@ -5327,22 +5477,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -5429,25 +5579,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>262</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>317</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>263</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="75"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="88"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B6" s="25" t="s">
@@ -5789,25 +5939,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
     </row>
     <row r="3" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="75"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="88"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B6" s="25" t="s">
@@ -6129,25 +6279,25 @@
       </c>
     </row>
     <row r="38" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="89" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
     </row>
     <row r="39" spans="2:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="90"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B41" s="74" t="s">
+      <c r="B41" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="78"/>
-      <c r="D41" s="75"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="88"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B42" s="25" t="s">
@@ -6520,6 +6670,1647 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{371F3650-624E-7A4C-9A5A-E52222BCB235}">
+  <dimension ref="B5:E161"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="30.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="81" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B6" s="83" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B8" s="85" t="s">
+        <v>325</v>
+      </c>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B9" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B10" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B11" s="49">
+        <v>1</v>
+      </c>
+      <c r="C11" s="49">
+        <v>7</v>
+      </c>
+      <c r="D11" s="49">
+        <v>3</v>
+      </c>
+      <c r="E11" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B12" s="50">
+        <v>2</v>
+      </c>
+      <c r="C12" s="50">
+        <v>-7</v>
+      </c>
+      <c r="D12" s="50">
+        <v>3</v>
+      </c>
+      <c r="E12" s="50">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B13" s="69">
+        <v>3</v>
+      </c>
+      <c r="C13" s="69">
+        <v>7</v>
+      </c>
+      <c r="D13" s="69">
+        <v>-3</v>
+      </c>
+      <c r="E13" s="69">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B14" s="50">
+        <v>4</v>
+      </c>
+      <c r="C14" s="50">
+        <v>-7</v>
+      </c>
+      <c r="D14" s="50">
+        <v>-3</v>
+      </c>
+      <c r="E14" s="50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B15" s="49">
+        <v>5</v>
+      </c>
+      <c r="C15" s="49">
+        <v>0</v>
+      </c>
+      <c r="D15" s="49">
+        <v>5</v>
+      </c>
+      <c r="E15" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B16" s="50">
+        <v>6</v>
+      </c>
+      <c r="C16" s="50">
+        <v>127</v>
+      </c>
+      <c r="D16" s="50">
+        <v>2</v>
+      </c>
+      <c r="E16" s="50">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B17" s="69">
+        <v>7</v>
+      </c>
+      <c r="C17" s="69">
+        <v>-128</v>
+      </c>
+      <c r="D17" s="69">
+        <v>2</v>
+      </c>
+      <c r="E17" s="69">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B18" s="50">
+        <v>8</v>
+      </c>
+      <c r="C18" s="50">
+        <v>-127</v>
+      </c>
+      <c r="D18" s="50">
+        <v>2</v>
+      </c>
+      <c r="E18" s="50">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B19" s="49">
+        <v>9</v>
+      </c>
+      <c r="C19" s="49">
+        <v>127</v>
+      </c>
+      <c r="D19" s="49">
+        <v>-2</v>
+      </c>
+      <c r="E19" s="49">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B20" s="50">
+        <v>10</v>
+      </c>
+      <c r="C20" s="50">
+        <v>7</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B21" s="69">
+        <v>11</v>
+      </c>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69">
+        <v>7</v>
+      </c>
+      <c r="E21" s="69"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B22" s="50">
+        <v>12</v>
+      </c>
+      <c r="C22" s="50">
+        <v>-128</v>
+      </c>
+      <c r="D22" s="50">
+        <v>-1</v>
+      </c>
+      <c r="E22" s="50">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B26" s="79" t="s">
+        <v>341</v>
+      </c>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B27" s="80" t="s">
+        <v>324</v>
+      </c>
+      <c r="C27" s="80"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B29" s="78" t="s">
+        <v>326</v>
+      </c>
+      <c r="C29" s="78"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="78"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B30" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C30" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D30" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E30" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B31" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C31" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D31" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E31" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B32" s="69">
+        <v>1</v>
+      </c>
+      <c r="C32" s="69">
+        <v>7</v>
+      </c>
+      <c r="D32" s="69">
+        <v>3</v>
+      </c>
+      <c r="E32" s="69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B33" s="70">
+        <v>2</v>
+      </c>
+      <c r="C33" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D33" s="70">
+        <v>3</v>
+      </c>
+      <c r="E33" s="70">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B34" s="69">
+        <v>3</v>
+      </c>
+      <c r="C34" s="69">
+        <v>7</v>
+      </c>
+      <c r="D34" s="69">
+        <v>-3</v>
+      </c>
+      <c r="E34" s="69">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B35" s="70">
+        <v>4</v>
+      </c>
+      <c r="C35" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D35" s="70">
+        <v>-3</v>
+      </c>
+      <c r="E35" s="70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B36" s="69">
+        <v>5</v>
+      </c>
+      <c r="C36" s="69">
+        <v>0</v>
+      </c>
+      <c r="D36" s="69">
+        <v>123</v>
+      </c>
+      <c r="E36" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B37" s="70">
+        <v>6</v>
+      </c>
+      <c r="C37" s="70">
+        <v>32767</v>
+      </c>
+      <c r="D37" s="70">
+        <v>2</v>
+      </c>
+      <c r="E37" s="70">
+        <v>16383</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B38" s="69">
+        <v>7</v>
+      </c>
+      <c r="C38" s="69">
+        <v>-32768</v>
+      </c>
+      <c r="D38" s="69">
+        <v>2</v>
+      </c>
+      <c r="E38" s="69">
+        <v>-16384</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B39" s="70">
+        <v>8</v>
+      </c>
+      <c r="C39" s="70">
+        <v>-32767</v>
+      </c>
+      <c r="D39" s="70">
+        <v>2</v>
+      </c>
+      <c r="E39" s="70">
+        <v>-16384</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B40" s="69">
+        <v>9</v>
+      </c>
+      <c r="C40" s="69">
+        <v>32767</v>
+      </c>
+      <c r="D40" s="69">
+        <v>-2</v>
+      </c>
+      <c r="E40" s="69">
+        <v>-16384</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B41" s="50">
+        <v>10</v>
+      </c>
+      <c r="C41" s="50">
+        <v>7</v>
+      </c>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B42" s="69">
+        <v>11</v>
+      </c>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69">
+        <v>7</v>
+      </c>
+      <c r="E42" s="69"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B43" s="50">
+        <v>12</v>
+      </c>
+      <c r="C43" s="50">
+        <v>-32768</v>
+      </c>
+      <c r="D43" s="50">
+        <v>-1</v>
+      </c>
+      <c r="E43" s="50">
+        <v>32768</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B44" s="75"/>
+      <c r="C44" s="75"/>
+      <c r="D44" s="75"/>
+      <c r="E44" s="75"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B47" s="79" t="s">
+        <v>327</v>
+      </c>
+      <c r="C47" s="79"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B48" s="80" t="s">
+        <v>324</v>
+      </c>
+      <c r="C48" s="80"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B50" s="78" t="s">
+        <v>328</v>
+      </c>
+      <c r="C50" s="78"/>
+      <c r="D50" s="78"/>
+      <c r="E50" s="78"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B51" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C51" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D51" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E51" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B52" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C52" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D52" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E52" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B53" s="69">
+        <v>1</v>
+      </c>
+      <c r="C53" s="69">
+        <v>7</v>
+      </c>
+      <c r="D53" s="69">
+        <v>3</v>
+      </c>
+      <c r="E53" s="69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B54" s="70">
+        <v>2</v>
+      </c>
+      <c r="C54" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D54" s="70">
+        <v>3</v>
+      </c>
+      <c r="E54" s="70">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B55" s="69">
+        <v>3</v>
+      </c>
+      <c r="C55" s="69">
+        <v>7</v>
+      </c>
+      <c r="D55" s="69">
+        <v>-3</v>
+      </c>
+      <c r="E55" s="69">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B56" s="70">
+        <v>4</v>
+      </c>
+      <c r="C56" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D56" s="70">
+        <v>-3</v>
+      </c>
+      <c r="E56" s="70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B57" s="69">
+        <v>5</v>
+      </c>
+      <c r="C57" s="69">
+        <v>0</v>
+      </c>
+      <c r="D57" s="69">
+        <v>5</v>
+      </c>
+      <c r="E57" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B58" s="70">
+        <v>6</v>
+      </c>
+      <c r="C58" s="70">
+        <v>2147483647</v>
+      </c>
+      <c r="D58" s="70">
+        <v>2</v>
+      </c>
+      <c r="E58" s="70">
+        <v>1073741823</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B59" s="69">
+        <v>7</v>
+      </c>
+      <c r="C59" s="69">
+        <v>-2147483648</v>
+      </c>
+      <c r="D59" s="69">
+        <v>2</v>
+      </c>
+      <c r="E59" s="69">
+        <v>-1073741824</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B60" s="70">
+        <v>8</v>
+      </c>
+      <c r="C60" s="70">
+        <v>-2147483647</v>
+      </c>
+      <c r="D60" s="70">
+        <v>2</v>
+      </c>
+      <c r="E60" s="70">
+        <v>-1073741824</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B61" s="69">
+        <v>9</v>
+      </c>
+      <c r="C61" s="69">
+        <v>2147483647</v>
+      </c>
+      <c r="D61" s="69">
+        <v>-2</v>
+      </c>
+      <c r="E61" s="69">
+        <v>-1073741824</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B62" s="50">
+        <v>10</v>
+      </c>
+      <c r="C62" s="50">
+        <v>7</v>
+      </c>
+      <c r="D62" s="50"/>
+      <c r="E62" s="50"/>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B63" s="69">
+        <v>11</v>
+      </c>
+      <c r="C63" s="69"/>
+      <c r="D63" s="69">
+        <v>7</v>
+      </c>
+      <c r="E63" s="69"/>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B67" s="79" t="s">
+        <v>329</v>
+      </c>
+      <c r="C67" s="79"/>
+      <c r="D67" s="79"/>
+      <c r="E67" s="79"/>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B68" s="80" t="s">
+        <v>324</v>
+      </c>
+      <c r="C68" s="80"/>
+      <c r="D68" s="80"/>
+      <c r="E68" s="80"/>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B70" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="C70" s="78"/>
+      <c r="D70" s="78"/>
+      <c r="E70" s="78"/>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B71" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C71" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D71" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E71" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B72" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C72" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D72" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E72" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B73" s="69">
+        <v>1</v>
+      </c>
+      <c r="C73" s="72" t="s">
+        <v>92</v>
+      </c>
+      <c r="D73" s="72" t="s">
+        <v>331</v>
+      </c>
+      <c r="E73" s="72" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B74" s="70">
+        <v>2</v>
+      </c>
+      <c r="C74" s="73" t="s">
+        <v>144</v>
+      </c>
+      <c r="D74" s="73" t="s">
+        <v>331</v>
+      </c>
+      <c r="E74" s="73" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B75" s="69">
+        <v>3</v>
+      </c>
+      <c r="C75" s="72" t="s">
+        <v>92</v>
+      </c>
+      <c r="D75" s="72" t="s">
+        <v>333</v>
+      </c>
+      <c r="E75" s="72" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B76" s="70">
+        <v>4</v>
+      </c>
+      <c r="C76" s="73" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" s="73" t="s">
+        <v>333</v>
+      </c>
+      <c r="E76" s="73" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B77" s="69">
+        <v>5</v>
+      </c>
+      <c r="C77" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" s="72" t="s">
+        <v>334</v>
+      </c>
+      <c r="E77" s="72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B78" s="70">
+        <v>6</v>
+      </c>
+      <c r="C78" s="73" t="s">
+        <v>335</v>
+      </c>
+      <c r="D78" s="73" t="s">
+        <v>332</v>
+      </c>
+      <c r="E78" s="73" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B79" s="69">
+        <v>7</v>
+      </c>
+      <c r="C79" s="72" t="s">
+        <v>337</v>
+      </c>
+      <c r="D79" s="72" t="s">
+        <v>332</v>
+      </c>
+      <c r="E79" s="72" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B80" s="70">
+        <v>8</v>
+      </c>
+      <c r="C80" s="73" t="s">
+        <v>339</v>
+      </c>
+      <c r="D80" s="73" t="s">
+        <v>332</v>
+      </c>
+      <c r="E80" s="73" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B81" s="69">
+        <v>9</v>
+      </c>
+      <c r="C81" s="72" t="s">
+        <v>335</v>
+      </c>
+      <c r="D81" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="E81" s="72" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B82" s="50">
+        <v>10</v>
+      </c>
+      <c r="C82" s="50">
+        <v>7</v>
+      </c>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B83" s="69">
+        <v>11</v>
+      </c>
+      <c r="C83" s="69"/>
+      <c r="D83" s="69">
+        <v>7</v>
+      </c>
+      <c r="E83" s="69"/>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B87" s="79" t="s">
+        <v>343</v>
+      </c>
+      <c r="C87" s="79"/>
+      <c r="D87" s="79"/>
+      <c r="E87" s="79"/>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B88" s="80" t="s">
+        <v>324</v>
+      </c>
+      <c r="C88" s="80"/>
+      <c r="D88" s="80"/>
+      <c r="E88" s="80"/>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B90" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="C90" s="78"/>
+      <c r="D90" s="78"/>
+      <c r="E90" s="78"/>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B91" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C91" s="74" t="s">
+        <v>321</v>
+      </c>
+      <c r="D91" s="74" t="s">
+        <v>281</v>
+      </c>
+      <c r="E91" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B92" s="74" t="s">
+        <v>323</v>
+      </c>
+      <c r="C92" s="74" t="s">
+        <v>321</v>
+      </c>
+      <c r="D92" s="74" t="s">
+        <v>281</v>
+      </c>
+      <c r="E92" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B93" s="69">
+        <v>1</v>
+      </c>
+      <c r="C93" s="69">
+        <v>7</v>
+      </c>
+      <c r="D93" s="69">
+        <v>3</v>
+      </c>
+      <c r="E93" s="69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B94" s="70">
+        <v>2</v>
+      </c>
+      <c r="C94" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D94" s="70">
+        <v>3</v>
+      </c>
+      <c r="E94" s="70">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B95" s="69">
+        <v>3</v>
+      </c>
+      <c r="C95" s="69">
+        <v>7</v>
+      </c>
+      <c r="D95" s="69">
+        <v>-3</v>
+      </c>
+      <c r="E95" s="69">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B96" s="70">
+        <v>4</v>
+      </c>
+      <c r="C96" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D96" s="70">
+        <v>-3</v>
+      </c>
+      <c r="E96" s="70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B97" s="69">
+        <v>5</v>
+      </c>
+      <c r="C97" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="D97" s="76" t="s">
+        <v>353</v>
+      </c>
+      <c r="E97" s="69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B98" s="70">
+        <v>6</v>
+      </c>
+      <c r="C98" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D98" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="E98" s="70">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B99" s="69">
+        <v>7</v>
+      </c>
+      <c r="C99" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="D99" s="76" t="s">
+        <v>351</v>
+      </c>
+      <c r="E99" s="69">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B100" s="70">
+        <v>8</v>
+      </c>
+      <c r="C100" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D100" s="77" t="s">
+        <v>351</v>
+      </c>
+      <c r="E100" s="70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B101" s="69">
+        <v>9</v>
+      </c>
+      <c r="C101" s="69">
+        <v>0</v>
+      </c>
+      <c r="D101" s="76" t="s">
+        <v>354</v>
+      </c>
+      <c r="E101" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B102" s="50">
+        <v>10</v>
+      </c>
+      <c r="C102" s="50">
+        <v>7</v>
+      </c>
+      <c r="D102" s="50"/>
+      <c r="E102" s="50"/>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B103" s="69">
+        <v>11</v>
+      </c>
+      <c r="C103" s="69"/>
+      <c r="D103" s="69">
+        <v>7</v>
+      </c>
+      <c r="E103" s="69"/>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B107" s="79" t="s">
+        <v>344</v>
+      </c>
+      <c r="C107" s="79"/>
+      <c r="D107" s="79"/>
+      <c r="E107" s="79"/>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B108" s="80" t="s">
+        <v>324</v>
+      </c>
+      <c r="C108" s="80"/>
+      <c r="D108" s="80"/>
+      <c r="E108" s="80"/>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B110" s="78" t="s">
+        <v>345</v>
+      </c>
+      <c r="C110" s="78"/>
+      <c r="D110" s="78"/>
+      <c r="E110" s="78"/>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B111" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C111" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D111" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E111" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B112" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C112" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D112" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E112" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B113" s="69">
+        <v>1</v>
+      </c>
+      <c r="C113" s="69">
+        <v>7</v>
+      </c>
+      <c r="D113" s="69">
+        <v>3</v>
+      </c>
+      <c r="E113" s="69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B114" s="70">
+        <v>2</v>
+      </c>
+      <c r="C114" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D114" s="70">
+        <v>3</v>
+      </c>
+      <c r="E114" s="70">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B115" s="69">
+        <v>3</v>
+      </c>
+      <c r="C115" s="69">
+        <v>7</v>
+      </c>
+      <c r="D115" s="69">
+        <v>-3</v>
+      </c>
+      <c r="E115" s="69">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B116" s="70">
+        <v>4</v>
+      </c>
+      <c r="C116" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D116" s="70">
+        <v>-3</v>
+      </c>
+      <c r="E116" s="70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B117" s="69">
+        <v>5</v>
+      </c>
+      <c r="C117" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="D117" s="76" t="s">
+        <v>353</v>
+      </c>
+      <c r="E117" s="69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B118" s="70">
+        <v>6</v>
+      </c>
+      <c r="C118" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D118" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="E118" s="70">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B119" s="69">
+        <v>7</v>
+      </c>
+      <c r="C119" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="D119" s="76" t="s">
+        <v>351</v>
+      </c>
+      <c r="E119" s="69">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B120" s="70">
+        <v>8</v>
+      </c>
+      <c r="C120" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D120" s="77" t="s">
+        <v>351</v>
+      </c>
+      <c r="E120" s="70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B121" s="69">
+        <v>9</v>
+      </c>
+      <c r="C121" s="69">
+        <v>0</v>
+      </c>
+      <c r="D121" s="76" t="s">
+        <v>354</v>
+      </c>
+      <c r="E121" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B127" s="79" t="s">
+        <v>346</v>
+      </c>
+      <c r="C127" s="79"/>
+      <c r="D127" s="79"/>
+      <c r="E127" s="79"/>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B128" s="80" t="s">
+        <v>324</v>
+      </c>
+      <c r="C128" s="80"/>
+      <c r="D128" s="80"/>
+      <c r="E128" s="80"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B130" s="78" t="s">
+        <v>347</v>
+      </c>
+      <c r="C130" s="78"/>
+      <c r="D130" s="78"/>
+      <c r="E130" s="78"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B131" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C131" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D131" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E131" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B132" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C132" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D132" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E132" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B133" s="69">
+        <v>1</v>
+      </c>
+      <c r="C133" s="69">
+        <v>7</v>
+      </c>
+      <c r="D133" s="69">
+        <v>3</v>
+      </c>
+      <c r="E133" s="69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B134" s="70">
+        <v>2</v>
+      </c>
+      <c r="C134" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D134" s="70">
+        <v>3</v>
+      </c>
+      <c r="E134" s="70">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B135" s="69">
+        <v>3</v>
+      </c>
+      <c r="C135" s="69">
+        <v>7</v>
+      </c>
+      <c r="D135" s="69">
+        <v>-3</v>
+      </c>
+      <c r="E135" s="69">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B136" s="70">
+        <v>4</v>
+      </c>
+      <c r="C136" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D136" s="70">
+        <v>-3</v>
+      </c>
+      <c r="E136" s="70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B137" s="69">
+        <v>5</v>
+      </c>
+      <c r="C137" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="D137" s="76" t="s">
+        <v>353</v>
+      </c>
+      <c r="E137" s="69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B138" s="70">
+        <v>6</v>
+      </c>
+      <c r="C138" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D138" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="E138" s="70">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B139" s="69">
+        <v>7</v>
+      </c>
+      <c r="C139" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="D139" s="76" t="s">
+        <v>351</v>
+      </c>
+      <c r="E139" s="69">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B140" s="70">
+        <v>8</v>
+      </c>
+      <c r="C140" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D140" s="77" t="s">
+        <v>351</v>
+      </c>
+      <c r="E140" s="70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B141" s="69">
+        <v>9</v>
+      </c>
+      <c r="C141" s="69">
+        <v>0</v>
+      </c>
+      <c r="D141" s="76" t="s">
+        <v>354</v>
+      </c>
+      <c r="E141" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B142" s="70">
+        <v>10</v>
+      </c>
+      <c r="C142" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="D142" s="73">
+        <v>97</v>
+      </c>
+      <c r="E142" s="73" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B143" s="69">
+        <v>11</v>
+      </c>
+      <c r="C143" s="72" t="s">
+        <v>356</v>
+      </c>
+      <c r="D143" s="72">
+        <v>97</v>
+      </c>
+      <c r="E143" s="72" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B147" s="79" t="s">
+        <v>348</v>
+      </c>
+      <c r="C147" s="79"/>
+      <c r="D147" s="79"/>
+      <c r="E147" s="79"/>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B148" s="80" t="s">
+        <v>324</v>
+      </c>
+      <c r="C148" s="80"/>
+      <c r="D148" s="80"/>
+      <c r="E148" s="80"/>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B150" s="78" t="s">
+        <v>349</v>
+      </c>
+      <c r="C150" s="78"/>
+      <c r="D150" s="78"/>
+      <c r="E150" s="78"/>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B151" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C151" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D151" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E151" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B152" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C152" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D152" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E152" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B153" s="69">
+        <v>1</v>
+      </c>
+      <c r="C153" s="69">
+        <v>7</v>
+      </c>
+      <c r="D153" s="69">
+        <v>3</v>
+      </c>
+      <c r="E153" s="69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B154" s="70">
+        <v>2</v>
+      </c>
+      <c r="C154" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D154" s="70">
+        <v>3</v>
+      </c>
+      <c r="E154" s="70">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B155" s="69">
+        <v>3</v>
+      </c>
+      <c r="C155" s="69">
+        <v>7</v>
+      </c>
+      <c r="D155" s="69">
+        <v>-3</v>
+      </c>
+      <c r="E155" s="69">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B156" s="70">
+        <v>4</v>
+      </c>
+      <c r="C156" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D156" s="70">
+        <v>-3</v>
+      </c>
+      <c r="E156" s="70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B157" s="69">
+        <v>5</v>
+      </c>
+      <c r="C157" s="69">
+        <v>0</v>
+      </c>
+      <c r="D157" s="69">
+        <v>97</v>
+      </c>
+      <c r="E157" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B158" s="70">
+        <v>6</v>
+      </c>
+      <c r="C158" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="D158" s="73">
+        <v>97</v>
+      </c>
+      <c r="E158" s="73" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B159" s="69">
+        <v>7</v>
+      </c>
+      <c r="C159" s="72" t="s">
+        <v>356</v>
+      </c>
+      <c r="D159" s="72">
+        <v>97</v>
+      </c>
+      <c r="E159" s="72" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B160" s="70">
+        <v>8</v>
+      </c>
+      <c r="C160" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="D160" s="73">
+        <v>-97</v>
+      </c>
+      <c r="E160" s="73" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B161" s="69">
+        <v>9</v>
+      </c>
+      <c r="C161" s="72" t="s">
+        <v>356</v>
+      </c>
+      <c r="D161" s="72">
+        <v>-97</v>
+      </c>
+      <c r="E161" s="72" t="s">
+        <v>357</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B150:E150"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B128:E128"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:E88"/>
@@ -6532,22 +8323,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>252</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -6642,22 +8433,22 @@
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>255</v>
       </c>
-      <c r="C20" s="76"/>
+      <c r="C20" s="89"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>256</v>
       </c>
-      <c r="C21" s="77"/>
+      <c r="C21" s="90"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>257</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="88"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -6751,22 +8542,22 @@
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="89" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="76"/>
+      <c r="C38" s="89"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="90" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="77"/>
+      <c r="C39" s="90"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="74" t="s">
+      <c r="B41" s="87" t="s">
         <v>243</v>
       </c>
-      <c r="C41" s="75"/>
+      <c r="C41" s="88"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B42" s="4" t="s">
@@ -6857,25 +8648,25 @@
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B56" s="76" t="s">
+      <c r="B56" s="89" t="s">
         <v>218</v>
       </c>
-      <c r="C56" s="76"/>
-      <c r="D56" s="76"/>
+      <c r="C56" s="89"/>
+      <c r="D56" s="89"/>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B57" s="77" t="s">
+      <c r="B57" s="90" t="s">
         <v>219</v>
       </c>
-      <c r="C57" s="77"/>
-      <c r="D57" s="77"/>
+      <c r="C57" s="90"/>
+      <c r="D57" s="90"/>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B59" s="74" t="s">
+      <c r="B59" s="87" t="s">
         <v>217</v>
       </c>
-      <c r="C59" s="78"/>
-      <c r="D59" s="75"/>
+      <c r="C59" s="91"/>
+      <c r="D59" s="88"/>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B60" s="25" t="s">
@@ -7226,22 +9017,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -7335,22 +9126,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="76"/>
+      <c r="C20" s="89"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="77"/>
+      <c r="C21" s="90"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="88"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -7444,22 +9235,22 @@
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="76"/>
+      <c r="C38" s="89"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="77"/>
+      <c r="C39" s="90"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="74" t="s">
+      <c r="B41" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="75"/>
+      <c r="C41" s="88"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B42" s="4" t="s">
@@ -7576,22 +9367,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -7682,22 +9473,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="76"/>
+      <c r="C20" s="89"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="77"/>
+      <c r="C21" s="90"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="88"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -7811,22 +9602,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -7917,22 +9708,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="C20" s="76"/>
+      <c r="C20" s="89"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>173</v>
       </c>
-      <c r="C21" s="77"/>
+      <c r="C21" s="90"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="88"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -8047,22 +9838,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -8153,22 +9944,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="76"/>
+      <c r="C20" s="89"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="77"/>
+      <c r="C21" s="90"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="88"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -8259,22 +10050,22 @@
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="76"/>
+      <c r="C38" s="89"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="77"/>
+      <c r="C39" s="90"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="74" t="s">
+      <c r="B41" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="75"/>
+      <c r="C41" s="88"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B42" s="4" t="s">
@@ -8391,22 +10182,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -8497,22 +10288,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>207</v>
       </c>
-      <c r="C20" s="76"/>
+      <c r="C20" s="89"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>208</v>
       </c>
-      <c r="C21" s="77"/>
+      <c r="C21" s="90"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>209</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="88"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">
@@ -8603,25 +10394,25 @@
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="89" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="90" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="90"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B41" s="74" t="s">
+      <c r="B41" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="78"/>
-      <c r="D41" s="75"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="88"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B42" s="25" t="s">
@@ -8970,22 +10761,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="92" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="79"/>
+      <c r="C2" s="92"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="93" t="s">
         <v>270</v>
       </c>
-      <c r="C3" s="80"/>
+      <c r="C3" s="93"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="94" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="82"/>
+      <c r="C5" s="95"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="58" t="s">
@@ -9076,22 +10867,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="B20" s="79" t="s">
+      <c r="B20" s="92" t="s">
         <v>169</v>
       </c>
-      <c r="C20" s="79"/>
+      <c r="C20" s="92"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="80" t="s">
+      <c r="B21" s="93" t="s">
         <v>170</v>
       </c>
-      <c r="C21" s="80"/>
+      <c r="C21" s="93"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="81" t="s">
+      <c r="B23" s="94" t="s">
         <v>171</v>
       </c>
-      <c r="C23" s="82"/>
+      <c r="C23" s="95"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="58" t="s">
@@ -9182,22 +10973,22 @@
       </c>
     </row>
     <row r="38" spans="2:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="B38" s="79" t="s">
+      <c r="B38" s="92" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="79"/>
+      <c r="C38" s="92"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="80" t="s">
+      <c r="B39" s="93" t="s">
         <v>108</v>
       </c>
-      <c r="C39" s="80"/>
+      <c r="C39" s="93"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="81" t="s">
+      <c r="B41" s="94" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="82"/>
+      <c r="C41" s="95"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B42" s="58" t="s">
@@ -9288,22 +11079,22 @@
       </c>
     </row>
     <row r="56" spans="2:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="B56" s="79" t="s">
+      <c r="B56" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="C56" s="79"/>
+      <c r="C56" s="92"/>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B57" s="80" t="s">
+      <c r="B57" s="93" t="s">
         <v>204</v>
       </c>
-      <c r="C57" s="80"/>
+      <c r="C57" s="93"/>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B59" s="81" t="s">
+      <c r="B59" s="94" t="s">
         <v>205</v>
       </c>
-      <c r="C59" s="82"/>
+      <c r="C59" s="95"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B60" s="58" t="s">
@@ -9394,31 +11185,31 @@
       </c>
     </row>
     <row r="74" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B74" s="70" t="s">
+      <c r="B74" s="81" t="s">
         <v>273</v>
       </c>
-      <c r="C74" s="71"/>
-      <c r="D74" s="71"/>
-      <c r="E74" s="71"/>
-      <c r="F74" s="71"/>
+      <c r="C74" s="82"/>
+      <c r="D74" s="82"/>
+      <c r="E74" s="82"/>
+      <c r="F74" s="82"/>
     </row>
     <row r="75" spans="2:6" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B75" s="83" t="s">
+      <c r="B75" s="96" t="s">
         <v>274</v>
       </c>
-      <c r="C75" s="84"/>
-      <c r="D75" s="84"/>
-      <c r="E75" s="84"/>
-      <c r="F75" s="84"/>
+      <c r="C75" s="97"/>
+      <c r="D75" s="97"/>
+      <c r="E75" s="97"/>
+      <c r="F75" s="97"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B77" s="85" t="s">
+      <c r="B77" s="98" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="86"/>
-      <c r="D77" s="86"/>
-      <c r="E77" s="86"/>
-      <c r="F77" s="87"/>
+      <c r="C77" s="99"/>
+      <c r="D77" s="99"/>
+      <c r="E77" s="99"/>
+      <c r="F77" s="100"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B78" s="59" t="s">
@@ -9821,22 +11612,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="89" t="s">
         <v>312</v>
       </c>
-      <c r="C2" s="76"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="90" t="s">
         <v>288</v>
       </c>
-      <c r="C3" s="77"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="87" t="s">
         <v>289</v>
       </c>
-      <c r="C5" s="75"/>
+      <c r="C5" s="88"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
@@ -9927,25 +11718,25 @@
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="89" t="s">
         <v>313</v>
       </c>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="90" t="s">
         <v>287</v>
       </c>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="90"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="78"/>
-      <c r="D23" s="75"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="88"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B24" s="4" t="s">

--- a/DEV/org.openl.rules.test/test-resources/functionality/Math.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/Math.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vpikus/Sources/OpenL/openl-tablets/DEV/org.openl.rules.test/test-resources/functionality/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4862A5FF-7075-6044-84E6-F3CB071E196C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498FC6F4-D6ED-FF48-9CE4-2075399052DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34980" windowHeight="22600" tabRatio="765" firstSheet="5" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2238,15 +2238,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2265,6 +2256,15 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2279,9 +2279,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2306,6 +2303,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3103,28 +3103,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="78" t="s">
         <v>282</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="3" spans="2:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="80" t="s">
         <v>283</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="82" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B6" s="47" t="s">
@@ -3331,28 +3331,28 @@
       <c r="E21" s="50"/>
     </row>
     <row r="25" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="78" t="s">
         <v>278</v>
       </c>
-      <c r="C25" s="82"/>
-      <c r="D25" s="82"/>
-      <c r="E25" s="82"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
     </row>
     <row r="26" spans="2:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="80" t="s">
         <v>280</v>
       </c>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B28" s="85" t="s">
+      <c r="B28" s="82" t="s">
         <v>277</v>
       </c>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B29" s="47" t="s">
@@ -6672,7 +6672,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{371F3650-624E-7A4C-9A5A-E52222BCB235}">
-  <dimension ref="B5:E161"/>
+  <dimension ref="B5:E159"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
@@ -6682,20 +6682,20 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="78" t="s">
         <v>340</v>
       </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="80" t="s">
         <v>324</v>
       </c>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B7" s="68"/>
@@ -6704,12 +6704,12 @@
       <c r="E7" s="68"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="82" t="s">
         <v>325</v>
       </c>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B9" s="47" t="s">
@@ -6886,52 +6886,52 @@
       <c r="E21" s="69"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B22" s="50">
-        <v>12</v>
-      </c>
-      <c r="C22" s="50">
-        <v>-128</v>
-      </c>
-      <c r="D22" s="50">
-        <v>-1</v>
-      </c>
-      <c r="E22" s="50">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="75"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B25" s="84" t="s">
+        <v>341</v>
+      </c>
+      <c r="C25" s="84"/>
+      <c r="D25" s="84"/>
+      <c r="E25" s="84"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B26" s="79" t="s">
-        <v>341</v>
-      </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B27" s="80" t="s">
+      <c r="B26" s="85" t="s">
         <v>324</v>
       </c>
-      <c r="C27" s="80"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B28" s="86" t="s">
+        <v>326</v>
+      </c>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B29" s="78" t="s">
-        <v>326</v>
-      </c>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
+      <c r="B29" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C29" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D29" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E29" s="71" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B30" s="71" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C30" s="71" t="s">
         <v>321</v>
@@ -6940,1371 +6940,1343 @@
         <v>281</v>
       </c>
       <c r="E30" s="71" t="s">
-        <v>0</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B31" s="71" t="s">
+      <c r="B31" s="69">
+        <v>1</v>
+      </c>
+      <c r="C31" s="69">
+        <v>7</v>
+      </c>
+      <c r="D31" s="69">
+        <v>3</v>
+      </c>
+      <c r="E31" s="69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B32" s="70">
+        <v>2</v>
+      </c>
+      <c r="C32" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D32" s="70">
+        <v>3</v>
+      </c>
+      <c r="E32" s="70">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B33" s="69">
+        <v>3</v>
+      </c>
+      <c r="C33" s="69">
+        <v>7</v>
+      </c>
+      <c r="D33" s="69">
+        <v>-3</v>
+      </c>
+      <c r="E33" s="69">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B34" s="70">
+        <v>4</v>
+      </c>
+      <c r="C34" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D34" s="70">
+        <v>-3</v>
+      </c>
+      <c r="E34" s="70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B35" s="69">
+        <v>5</v>
+      </c>
+      <c r="C35" s="69">
+        <v>0</v>
+      </c>
+      <c r="D35" s="69">
+        <v>123</v>
+      </c>
+      <c r="E35" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B36" s="70">
+        <v>6</v>
+      </c>
+      <c r="C36" s="70">
+        <v>32767</v>
+      </c>
+      <c r="D36" s="70">
+        <v>2</v>
+      </c>
+      <c r="E36" s="70">
+        <v>16383</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B37" s="69">
+        <v>7</v>
+      </c>
+      <c r="C37" s="69">
+        <v>-32768</v>
+      </c>
+      <c r="D37" s="69">
+        <v>2</v>
+      </c>
+      <c r="E37" s="69">
+        <v>-16384</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B38" s="70">
+        <v>8</v>
+      </c>
+      <c r="C38" s="70">
+        <v>-32767</v>
+      </c>
+      <c r="D38" s="70">
+        <v>2</v>
+      </c>
+      <c r="E38" s="70">
+        <v>-16384</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B39" s="69">
+        <v>9</v>
+      </c>
+      <c r="C39" s="69">
+        <v>32767</v>
+      </c>
+      <c r="D39" s="69">
+        <v>-2</v>
+      </c>
+      <c r="E39" s="69">
+        <v>-16384</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B40" s="50">
+        <v>10</v>
+      </c>
+      <c r="C40" s="50">
+        <v>7</v>
+      </c>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B41" s="69">
+        <v>11</v>
+      </c>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69">
+        <v>7</v>
+      </c>
+      <c r="E41" s="69"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B42" s="75"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="75"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B45" s="84" t="s">
+        <v>327</v>
+      </c>
+      <c r="C45" s="84"/>
+      <c r="D45" s="84"/>
+      <c r="E45" s="84"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B46" s="85" t="s">
+        <v>324</v>
+      </c>
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B48" s="86" t="s">
+        <v>328</v>
+      </c>
+      <c r="C48" s="86"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="86"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B49" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C49" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D49" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E49" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B50" s="71" t="s">
         <v>323</v>
       </c>
-      <c r="C31" s="71" t="s">
+      <c r="C50" s="71" t="s">
         <v>321</v>
       </c>
-      <c r="D31" s="71" t="s">
+      <c r="D50" s="71" t="s">
         <v>281</v>
       </c>
-      <c r="E31" s="71" t="s">
+      <c r="E50" s="71" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B32" s="69">
-        <v>1</v>
-      </c>
-      <c r="C32" s="69">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B51" s="69">
+        <v>1</v>
+      </c>
+      <c r="C51" s="69">
         <v>7</v>
       </c>
-      <c r="D32" s="69">
+      <c r="D51" s="69">
         <v>3</v>
       </c>
-      <c r="E32" s="69">
+      <c r="E51" s="69">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B33" s="70">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B52" s="70">
         <v>2</v>
       </c>
-      <c r="C33" s="70">
+      <c r="C52" s="70">
         <v>-7</v>
       </c>
-      <c r="D33" s="70">
+      <c r="D52" s="70">
         <v>3</v>
       </c>
-      <c r="E33" s="70">
+      <c r="E52" s="70">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B34" s="69">
-        <v>3</v>
-      </c>
-      <c r="C34" s="69">
-        <v>7</v>
-      </c>
-      <c r="D34" s="69">
-        <v>-3</v>
-      </c>
-      <c r="E34" s="69">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B35" s="70">
-        <v>4</v>
-      </c>
-      <c r="C35" s="70">
-        <v>-7</v>
-      </c>
-      <c r="D35" s="70">
-        <v>-3</v>
-      </c>
-      <c r="E35" s="70">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B36" s="69">
-        <v>5</v>
-      </c>
-      <c r="C36" s="69">
-        <v>0</v>
-      </c>
-      <c r="D36" s="69">
-        <v>123</v>
-      </c>
-      <c r="E36" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B37" s="70">
-        <v>6</v>
-      </c>
-      <c r="C37" s="70">
-        <v>32767</v>
-      </c>
-      <c r="D37" s="70">
-        <v>2</v>
-      </c>
-      <c r="E37" s="70">
-        <v>16383</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B38" s="69">
-        <v>7</v>
-      </c>
-      <c r="C38" s="69">
-        <v>-32768</v>
-      </c>
-      <c r="D38" s="69">
-        <v>2</v>
-      </c>
-      <c r="E38" s="69">
-        <v>-16384</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B39" s="70">
-        <v>8</v>
-      </c>
-      <c r="C39" s="70">
-        <v>-32767</v>
-      </c>
-      <c r="D39" s="70">
-        <v>2</v>
-      </c>
-      <c r="E39" s="70">
-        <v>-16384</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B40" s="69">
-        <v>9</v>
-      </c>
-      <c r="C40" s="69">
-        <v>32767</v>
-      </c>
-      <c r="D40" s="69">
-        <v>-2</v>
-      </c>
-      <c r="E40" s="69">
-        <v>-16384</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B41" s="50">
-        <v>10</v>
-      </c>
-      <c r="C41" s="50">
-        <v>7</v>
-      </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B42" s="69">
-        <v>11</v>
-      </c>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69">
-        <v>7</v>
-      </c>
-      <c r="E42" s="69"/>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B43" s="50">
-        <v>12</v>
-      </c>
-      <c r="C43" s="50">
-        <v>-32768</v>
-      </c>
-      <c r="D43" s="50">
-        <v>-1</v>
-      </c>
-      <c r="E43" s="50">
-        <v>32768</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B44" s="75"/>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="75"/>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B47" s="79" t="s">
-        <v>327</v>
-      </c>
-      <c r="C47" s="79"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="79"/>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B48" s="80" t="s">
-        <v>324</v>
-      </c>
-      <c r="C48" s="80"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="80"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B50" s="78" t="s">
-        <v>328</v>
-      </c>
-      <c r="C50" s="78"/>
-      <c r="D50" s="78"/>
-      <c r="E50" s="78"/>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B51" s="71" t="s">
-        <v>316</v>
-      </c>
-      <c r="C51" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D51" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E51" s="71" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B52" s="71" t="s">
-        <v>323</v>
-      </c>
-      <c r="C52" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D52" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E52" s="71" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B53" s="69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53" s="69">
         <v>7</v>
       </c>
       <c r="D53" s="69">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E53" s="69">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B54" s="70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" s="70">
         <v>-7</v>
       </c>
       <c r="D54" s="70">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E54" s="70">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B55" s="69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C55" s="69">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D55" s="69">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="E55" s="69">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B56" s="70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C56" s="70">
-        <v>-7</v>
+        <v>2147483647</v>
       </c>
       <c r="D56" s="70">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="E56" s="70">
-        <v>2</v>
+        <v>1073741823</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B57" s="69">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C57" s="69">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D57" s="69">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E57" s="69">
-        <v>0</v>
+        <v>-1073741824</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B58" s="70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C58" s="70">
-        <v>2147483647</v>
+        <v>-2147483647</v>
       </c>
       <c r="D58" s="70">
         <v>2</v>
       </c>
       <c r="E58" s="70">
-        <v>1073741823</v>
+        <v>-1073741824</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B59" s="69">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C59" s="69">
-        <v>-2147483648</v>
+        <v>2147483647</v>
       </c>
       <c r="D59" s="69">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="E59" s="69">
         <v>-1073741824</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B60" s="70">
-        <v>8</v>
-      </c>
-      <c r="C60" s="70">
-        <v>-2147483647</v>
-      </c>
-      <c r="D60" s="70">
-        <v>2</v>
-      </c>
-      <c r="E60" s="70">
-        <v>-1073741824</v>
-      </c>
+      <c r="B60" s="50">
+        <v>10</v>
+      </c>
+      <c r="C60" s="50">
+        <v>7</v>
+      </c>
+      <c r="D60" s="50"/>
+      <c r="E60" s="50"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B61" s="69">
-        <v>9</v>
-      </c>
-      <c r="C61" s="69">
-        <v>2147483647</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C61" s="69"/>
       <c r="D61" s="69">
-        <v>-2</v>
-      </c>
-      <c r="E61" s="69">
-        <v>-1073741824</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B62" s="50">
-        <v>10</v>
-      </c>
-      <c r="C62" s="50">
         <v>7</v>
       </c>
-      <c r="D62" s="50"/>
-      <c r="E62" s="50"/>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B63" s="69">
-        <v>11</v>
-      </c>
-      <c r="C63" s="69"/>
-      <c r="D63" s="69">
-        <v>7</v>
-      </c>
-      <c r="E63" s="69"/>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B67" s="79" t="s">
+      <c r="E61" s="69"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B65" s="84" t="s">
         <v>329</v>
       </c>
-      <c r="C67" s="79"/>
-      <c r="D67" s="79"/>
-      <c r="E67" s="79"/>
+      <c r="C65" s="84"/>
+      <c r="D65" s="84"/>
+      <c r="E65" s="84"/>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B66" s="85" t="s">
+        <v>324</v>
+      </c>
+      <c r="C66" s="85"/>
+      <c r="D66" s="85"/>
+      <c r="E66" s="85"/>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B68" s="80" t="s">
-        <v>324</v>
-      </c>
-      <c r="C68" s="80"/>
-      <c r="D68" s="80"/>
-      <c r="E68" s="80"/>
+      <c r="B68" s="86" t="s">
+        <v>330</v>
+      </c>
+      <c r="C68" s="86"/>
+      <c r="D68" s="86"/>
+      <c r="E68" s="86"/>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B69" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C69" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D69" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E69" s="71" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B70" s="78" t="s">
-        <v>330</v>
-      </c>
-      <c r="C70" s="78"/>
-      <c r="D70" s="78"/>
-      <c r="E70" s="78"/>
+      <c r="B70" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C70" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D70" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E70" s="71" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B71" s="71" t="s">
-        <v>316</v>
-      </c>
-      <c r="C71" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D71" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E71" s="71" t="s">
-        <v>0</v>
+      <c r="B71" s="69">
+        <v>1</v>
+      </c>
+      <c r="C71" s="72" t="s">
+        <v>92</v>
+      </c>
+      <c r="D71" s="72" t="s">
+        <v>331</v>
+      </c>
+      <c r="E71" s="72" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B72" s="71" t="s">
-        <v>323</v>
-      </c>
-      <c r="C72" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D72" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E72" s="71" t="s">
-        <v>322</v>
+      <c r="B72" s="70">
+        <v>2</v>
+      </c>
+      <c r="C72" s="73" t="s">
+        <v>144</v>
+      </c>
+      <c r="D72" s="73" t="s">
+        <v>331</v>
+      </c>
+      <c r="E72" s="73" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B73" s="69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" s="72" t="s">
         <v>92</v>
       </c>
       <c r="D73" s="72" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E73" s="72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B74" s="70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C74" s="73" t="s">
         <v>144</v>
       </c>
       <c r="D74" s="73" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E74" s="73" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B75" s="69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C75" s="72" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="D75" s="72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E75" s="72" t="s">
-        <v>333</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B76" s="70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C76" s="73" t="s">
-        <v>144</v>
+        <v>335</v>
       </c>
       <c r="D76" s="73" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E76" s="73" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B77" s="69">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C77" s="72" t="s">
-        <v>24</v>
+        <v>337</v>
       </c>
       <c r="D77" s="72" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E77" s="72" t="s">
-        <v>24</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B78" s="70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C78" s="73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D78" s="73" t="s">
         <v>332</v>
       </c>
       <c r="E78" s="73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B79" s="69">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C79" s="72" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D79" s="72" t="s">
-        <v>332</v>
+        <v>63</v>
       </c>
       <c r="E79" s="72" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B80" s="70">
-        <v>8</v>
-      </c>
-      <c r="C80" s="73" t="s">
-        <v>339</v>
-      </c>
-      <c r="D80" s="73" t="s">
-        <v>332</v>
-      </c>
-      <c r="E80" s="73" t="s">
-        <v>338</v>
-      </c>
+      <c r="B80" s="50">
+        <v>10</v>
+      </c>
+      <c r="C80" s="50">
+        <v>7</v>
+      </c>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B81" s="69">
-        <v>9</v>
-      </c>
-      <c r="C81" s="72" t="s">
-        <v>335</v>
-      </c>
-      <c r="D81" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="E81" s="72" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B82" s="50">
-        <v>10</v>
-      </c>
-      <c r="C82" s="50">
+        <v>11</v>
+      </c>
+      <c r="C81" s="69"/>
+      <c r="D81" s="69">
         <v>7</v>
       </c>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B83" s="69">
-        <v>11</v>
-      </c>
-      <c r="C83" s="69"/>
-      <c r="D83" s="69">
+      <c r="E81" s="69"/>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B85" s="84" t="s">
+        <v>343</v>
+      </c>
+      <c r="C85" s="84"/>
+      <c r="D85" s="84"/>
+      <c r="E85" s="84"/>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B86" s="85" t="s">
+        <v>324</v>
+      </c>
+      <c r="C86" s="85"/>
+      <c r="D86" s="85"/>
+      <c r="E86" s="85"/>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B88" s="86" t="s">
+        <v>342</v>
+      </c>
+      <c r="C88" s="86"/>
+      <c r="D88" s="86"/>
+      <c r="E88" s="86"/>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B89" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C89" s="74" t="s">
+        <v>321</v>
+      </c>
+      <c r="D89" s="74" t="s">
+        <v>281</v>
+      </c>
+      <c r="E89" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B90" s="74" t="s">
+        <v>323</v>
+      </c>
+      <c r="C90" s="74" t="s">
+        <v>321</v>
+      </c>
+      <c r="D90" s="74" t="s">
+        <v>281</v>
+      </c>
+      <c r="E90" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B91" s="69">
+        <v>1</v>
+      </c>
+      <c r="C91" s="69">
         <v>7</v>
       </c>
-      <c r="E83" s="69"/>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B87" s="79" t="s">
-        <v>343</v>
-      </c>
-      <c r="C87" s="79"/>
-      <c r="D87" s="79"/>
-      <c r="E87" s="79"/>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B88" s="80" t="s">
-        <v>324</v>
-      </c>
-      <c r="C88" s="80"/>
-      <c r="D88" s="80"/>
-      <c r="E88" s="80"/>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B90" s="78" t="s">
-        <v>342</v>
-      </c>
-      <c r="C90" s="78"/>
-      <c r="D90" s="78"/>
-      <c r="E90" s="78"/>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B91" s="71" t="s">
-        <v>316</v>
-      </c>
-      <c r="C91" s="74" t="s">
-        <v>321</v>
-      </c>
-      <c r="D91" s="74" t="s">
-        <v>281</v>
-      </c>
-      <c r="E91" s="71" t="s">
-        <v>0</v>
+      <c r="D91" s="69">
+        <v>3</v>
+      </c>
+      <c r="E91" s="69">
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B92" s="74" t="s">
-        <v>323</v>
-      </c>
-      <c r="C92" s="74" t="s">
-        <v>321</v>
-      </c>
-      <c r="D92" s="74" t="s">
-        <v>281</v>
-      </c>
-      <c r="E92" s="71" t="s">
-        <v>322</v>
+      <c r="B92" s="70">
+        <v>2</v>
+      </c>
+      <c r="C92" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D92" s="70">
+        <v>3</v>
+      </c>
+      <c r="E92" s="70">
+        <v>-3</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B93" s="69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" s="69">
         <v>7</v>
       </c>
       <c r="D93" s="69">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E93" s="69">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B94" s="70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C94" s="70">
         <v>-7</v>
       </c>
       <c r="D94" s="70">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E94" s="70">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B95" s="69">
-        <v>3</v>
-      </c>
-      <c r="C95" s="69">
-        <v>7</v>
-      </c>
-      <c r="D95" s="69">
-        <v>-3</v>
+        <v>5</v>
+      </c>
+      <c r="C95" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="D95" s="76" t="s">
+        <v>353</v>
       </c>
       <c r="E95" s="69">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B96" s="70">
-        <v>4</v>
-      </c>
-      <c r="C96" s="70">
-        <v>-7</v>
-      </c>
-      <c r="D96" s="70">
-        <v>-3</v>
+        <v>6</v>
+      </c>
+      <c r="C96" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D96" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="E96" s="70">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B97" s="69">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C97" s="76" t="s">
         <v>352</v>
       </c>
       <c r="D97" s="76" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E97" s="69">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B98" s="70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C98" s="77" t="s">
         <v>350</v>
       </c>
       <c r="D98" s="77" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E98" s="70">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B99" s="69">
+        <v>9</v>
+      </c>
+      <c r="C99" s="69">
+        <v>0</v>
+      </c>
+      <c r="D99" s="76" t="s">
+        <v>354</v>
+      </c>
+      <c r="E99" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B100" s="50">
+        <v>10</v>
+      </c>
+      <c r="C100" s="50">
         <v>7</v>
       </c>
-      <c r="C99" s="76" t="s">
-        <v>352</v>
-      </c>
-      <c r="D99" s="76" t="s">
-        <v>351</v>
-      </c>
-      <c r="E99" s="69">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B100" s="70">
-        <v>8</v>
-      </c>
-      <c r="C100" s="77" t="s">
-        <v>350</v>
-      </c>
-      <c r="D100" s="77" t="s">
-        <v>351</v>
-      </c>
-      <c r="E100" s="70">
-        <v>1</v>
-      </c>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B101" s="69">
-        <v>9</v>
-      </c>
-      <c r="C101" s="69">
-        <v>0</v>
-      </c>
-      <c r="D101" s="76" t="s">
-        <v>354</v>
-      </c>
-      <c r="E101" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B102" s="50">
-        <v>10</v>
-      </c>
-      <c r="C102" s="50">
+        <v>11</v>
+      </c>
+      <c r="C101" s="69"/>
+      <c r="D101" s="69">
         <v>7</v>
       </c>
-      <c r="D102" s="50"/>
-      <c r="E102" s="50"/>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B103" s="69">
-        <v>11</v>
-      </c>
-      <c r="C103" s="69"/>
-      <c r="D103" s="69">
+      <c r="E101" s="69"/>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B105" s="84" t="s">
+        <v>344</v>
+      </c>
+      <c r="C105" s="84"/>
+      <c r="D105" s="84"/>
+      <c r="E105" s="84"/>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B106" s="85" t="s">
+        <v>324</v>
+      </c>
+      <c r="C106" s="85"/>
+      <c r="D106" s="85"/>
+      <c r="E106" s="85"/>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B108" s="86" t="s">
+        <v>345</v>
+      </c>
+      <c r="C108" s="86"/>
+      <c r="D108" s="86"/>
+      <c r="E108" s="86"/>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B109" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C109" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D109" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E109" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B110" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C110" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D110" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E110" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B111" s="69">
+        <v>1</v>
+      </c>
+      <c r="C111" s="69">
         <v>7</v>
       </c>
-      <c r="E103" s="69"/>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B107" s="79" t="s">
-        <v>344</v>
-      </c>
-      <c r="C107" s="79"/>
-      <c r="D107" s="79"/>
-      <c r="E107" s="79"/>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B108" s="80" t="s">
-        <v>324</v>
-      </c>
-      <c r="C108" s="80"/>
-      <c r="D108" s="80"/>
-      <c r="E108" s="80"/>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B110" s="78" t="s">
-        <v>345</v>
-      </c>
-      <c r="C110" s="78"/>
-      <c r="D110" s="78"/>
-      <c r="E110" s="78"/>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B111" s="71" t="s">
-        <v>316</v>
-      </c>
-      <c r="C111" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D111" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E111" s="71" t="s">
-        <v>0</v>
+      <c r="D111" s="69">
+        <v>3</v>
+      </c>
+      <c r="E111" s="69">
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B112" s="71" t="s">
-        <v>323</v>
-      </c>
-      <c r="C112" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D112" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E112" s="71" t="s">
-        <v>322</v>
+      <c r="B112" s="70">
+        <v>2</v>
+      </c>
+      <c r="C112" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D112" s="70">
+        <v>3</v>
+      </c>
+      <c r="E112" s="70">
+        <v>-3</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B113" s="69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C113" s="69">
         <v>7</v>
       </c>
       <c r="D113" s="69">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E113" s="69">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B114" s="70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C114" s="70">
         <v>-7</v>
       </c>
       <c r="D114" s="70">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E114" s="70">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B115" s="69">
-        <v>3</v>
-      </c>
-      <c r="C115" s="69">
-        <v>7</v>
-      </c>
-      <c r="D115" s="69">
-        <v>-3</v>
+        <v>5</v>
+      </c>
+      <c r="C115" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="D115" s="76" t="s">
+        <v>353</v>
       </c>
       <c r="E115" s="69">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B116" s="70">
-        <v>4</v>
-      </c>
-      <c r="C116" s="70">
-        <v>-7</v>
-      </c>
-      <c r="D116" s="70">
-        <v>-3</v>
+        <v>6</v>
+      </c>
+      <c r="C116" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D116" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="E116" s="70">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B117" s="69">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C117" s="76" t="s">
         <v>352</v>
       </c>
       <c r="D117" s="76" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E117" s="69">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B118" s="70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C118" s="77" t="s">
         <v>350</v>
       </c>
       <c r="D118" s="77" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E118" s="70">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B119" s="69">
+        <v>9</v>
+      </c>
+      <c r="C119" s="69">
+        <v>0</v>
+      </c>
+      <c r="D119" s="76" t="s">
+        <v>354</v>
+      </c>
+      <c r="E119" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B125" s="84" t="s">
+        <v>346</v>
+      </c>
+      <c r="C125" s="84"/>
+      <c r="D125" s="84"/>
+      <c r="E125" s="84"/>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B126" s="85" t="s">
+        <v>324</v>
+      </c>
+      <c r="C126" s="85"/>
+      <c r="D126" s="85"/>
+      <c r="E126" s="85"/>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B128" s="86" t="s">
+        <v>347</v>
+      </c>
+      <c r="C128" s="86"/>
+      <c r="D128" s="86"/>
+      <c r="E128" s="86"/>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B129" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C129" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D129" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E129" s="71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B130" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C130" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D130" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E130" s="71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B131" s="69">
+        <v>1</v>
+      </c>
+      <c r="C131" s="69">
         <v>7</v>
       </c>
-      <c r="C119" s="76" t="s">
-        <v>352</v>
-      </c>
-      <c r="D119" s="76" t="s">
-        <v>351</v>
-      </c>
-      <c r="E119" s="69">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B120" s="70">
-        <v>8</v>
-      </c>
-      <c r="C120" s="77" t="s">
-        <v>350</v>
-      </c>
-      <c r="D120" s="77" t="s">
-        <v>351</v>
-      </c>
-      <c r="E120" s="70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B121" s="69">
-        <v>9</v>
-      </c>
-      <c r="C121" s="69">
-        <v>0</v>
-      </c>
-      <c r="D121" s="76" t="s">
-        <v>354</v>
-      </c>
-      <c r="E121" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B127" s="79" t="s">
-        <v>346</v>
-      </c>
-      <c r="C127" s="79"/>
-      <c r="D127" s="79"/>
-      <c r="E127" s="79"/>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B128" s="80" t="s">
-        <v>324</v>
-      </c>
-      <c r="C128" s="80"/>
-      <c r="D128" s="80"/>
-      <c r="E128" s="80"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B130" s="78" t="s">
-        <v>347</v>
-      </c>
-      <c r="C130" s="78"/>
-      <c r="D130" s="78"/>
-      <c r="E130" s="78"/>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B131" s="71" t="s">
-        <v>316</v>
-      </c>
-      <c r="C131" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D131" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E131" s="71" t="s">
-        <v>0</v>
+      <c r="D131" s="69">
+        <v>3</v>
+      </c>
+      <c r="E131" s="69">
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B132" s="71" t="s">
-        <v>323</v>
-      </c>
-      <c r="C132" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D132" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E132" s="71" t="s">
-        <v>322</v>
+      <c r="B132" s="70">
+        <v>2</v>
+      </c>
+      <c r="C132" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D132" s="70">
+        <v>3</v>
+      </c>
+      <c r="E132" s="70">
+        <v>-3</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B133" s="69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C133" s="69">
         <v>7</v>
       </c>
       <c r="D133" s="69">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E133" s="69">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B134" s="70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C134" s="70">
         <v>-7</v>
       </c>
       <c r="D134" s="70">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E134" s="70">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B135" s="69">
-        <v>3</v>
-      </c>
-      <c r="C135" s="69">
-        <v>7</v>
-      </c>
-      <c r="D135" s="69">
-        <v>-3</v>
+        <v>5</v>
+      </c>
+      <c r="C135" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="D135" s="76" t="s">
+        <v>353</v>
       </c>
       <c r="E135" s="69">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B136" s="70">
-        <v>4</v>
-      </c>
-      <c r="C136" s="70">
-        <v>-7</v>
-      </c>
-      <c r="D136" s="70">
-        <v>-3</v>
+        <v>6</v>
+      </c>
+      <c r="C136" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D136" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="E136" s="70">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B137" s="69">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C137" s="76" t="s">
         <v>352</v>
       </c>
       <c r="D137" s="76" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E137" s="69">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B138" s="70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C138" s="77" t="s">
         <v>350</v>
       </c>
       <c r="D138" s="77" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E138" s="70">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B139" s="69">
-        <v>7</v>
-      </c>
-      <c r="C139" s="76" t="s">
-        <v>352</v>
+        <v>9</v>
+      </c>
+      <c r="C139" s="69">
+        <v>0</v>
       </c>
       <c r="D139" s="76" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E139" s="69">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B140" s="70">
-        <v>8</v>
-      </c>
-      <c r="C140" s="77" t="s">
-        <v>350</v>
-      </c>
-      <c r="D140" s="77" t="s">
-        <v>351</v>
-      </c>
-      <c r="E140" s="70">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C140" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="D140" s="73">
+        <v>97</v>
+      </c>
+      <c r="E140" s="73" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B141" s="69">
-        <v>9</v>
-      </c>
-      <c r="C141" s="69">
-        <v>0</v>
-      </c>
-      <c r="D141" s="76" t="s">
-        <v>354</v>
-      </c>
-      <c r="E141" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B142" s="70">
-        <v>10</v>
-      </c>
-      <c r="C142" s="73" t="s">
-        <v>355</v>
-      </c>
-      <c r="D142" s="73">
+        <v>11</v>
+      </c>
+      <c r="C141" s="72" t="s">
+        <v>356</v>
+      </c>
+      <c r="D141" s="72">
         <v>97</v>
       </c>
-      <c r="E142" s="73" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B143" s="69">
-        <v>11</v>
-      </c>
-      <c r="C143" s="72" t="s">
-        <v>356</v>
-      </c>
-      <c r="D143" s="72">
-        <v>97</v>
-      </c>
-      <c r="E143" s="72" t="s">
+      <c r="E141" s="72" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B147" s="79" t="s">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B145" s="84" t="s">
         <v>348</v>
       </c>
-      <c r="C147" s="79"/>
-      <c r="D147" s="79"/>
-      <c r="E147" s="79"/>
+      <c r="C145" s="84"/>
+      <c r="D145" s="84"/>
+      <c r="E145" s="84"/>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B146" s="85" t="s">
+        <v>324</v>
+      </c>
+      <c r="C146" s="85"/>
+      <c r="D146" s="85"/>
+      <c r="E146" s="85"/>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B148" s="80" t="s">
-        <v>324</v>
-      </c>
-      <c r="C148" s="80"/>
-      <c r="D148" s="80"/>
-      <c r="E148" s="80"/>
+      <c r="B148" s="86" t="s">
+        <v>349</v>
+      </c>
+      <c r="C148" s="86"/>
+      <c r="D148" s="86"/>
+      <c r="E148" s="86"/>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B149" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C149" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D149" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E149" s="71" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B150" s="78" t="s">
-        <v>349</v>
-      </c>
-      <c r="C150" s="78"/>
-      <c r="D150" s="78"/>
-      <c r="E150" s="78"/>
+      <c r="B150" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="C150" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D150" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="E150" s="71" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B151" s="71" t="s">
-        <v>316</v>
-      </c>
-      <c r="C151" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D151" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E151" s="71" t="s">
-        <v>0</v>
+      <c r="B151" s="69">
+        <v>1</v>
+      </c>
+      <c r="C151" s="69">
+        <v>7</v>
+      </c>
+      <c r="D151" s="69">
+        <v>3</v>
+      </c>
+      <c r="E151" s="69">
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B152" s="71" t="s">
-        <v>323</v>
-      </c>
-      <c r="C152" s="71" t="s">
-        <v>321</v>
-      </c>
-      <c r="D152" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E152" s="71" t="s">
-        <v>322</v>
+      <c r="B152" s="70">
+        <v>2</v>
+      </c>
+      <c r="C152" s="70">
+        <v>-7</v>
+      </c>
+      <c r="D152" s="70">
+        <v>3</v>
+      </c>
+      <c r="E152" s="70">
+        <v>-3</v>
       </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B153" s="69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C153" s="69">
         <v>7</v>
       </c>
       <c r="D153" s="69">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E153" s="69">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B154" s="70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C154" s="70">
         <v>-7</v>
       </c>
       <c r="D154" s="70">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E154" s="70">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B155" s="69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C155" s="69">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D155" s="69">
-        <v>-3</v>
+        <v>97</v>
       </c>
       <c r="E155" s="69">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B156" s="70">
-        <v>4</v>
-      </c>
-      <c r="C156" s="70">
-        <v>-7</v>
-      </c>
-      <c r="D156" s="70">
-        <v>-3</v>
-      </c>
-      <c r="E156" s="70">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="C156" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="D156" s="73">
+        <v>97</v>
+      </c>
+      <c r="E156" s="73" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B157" s="69">
-        <v>5</v>
-      </c>
-      <c r="C157" s="69">
-        <v>0</v>
-      </c>
-      <c r="D157" s="69">
+        <v>7</v>
+      </c>
+      <c r="C157" s="72" t="s">
+        <v>356</v>
+      </c>
+      <c r="D157" s="72">
         <v>97</v>
       </c>
-      <c r="E157" s="69">
-        <v>0</v>
+      <c r="E157" s="72" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B158" s="70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C158" s="73" t="s">
         <v>355</v>
       </c>
       <c r="D158" s="73">
-        <v>97</v>
+        <v>-97</v>
       </c>
       <c r="E158" s="73" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B159" s="69">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C159" s="72" t="s">
         <v>356</v>
       </c>
       <c r="D159" s="72">
-        <v>97</v>
+        <v>-97</v>
       </c>
       <c r="E159" s="72" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B160" s="70">
-        <v>8</v>
-      </c>
-      <c r="C160" s="73" t="s">
-        <v>355</v>
-      </c>
-      <c r="D160" s="73">
-        <v>-97</v>
-      </c>
-      <c r="E160" s="73" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B161" s="69">
-        <v>9</v>
-      </c>
-      <c r="C161" s="72" t="s">
-        <v>356</v>
-      </c>
-      <c r="D161" s="72">
-        <v>-97</v>
-      </c>
-      <c r="E161" s="72" t="s">
         <v>357</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B65:E65"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B25:E25"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B150:E150"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B128:E128"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -10761,22 +10733,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="100" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="92"/>
+      <c r="C2" s="100"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="92" t="s">
         <v>270</v>
       </c>
-      <c r="C3" s="93"/>
+      <c r="C3" s="92"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="93" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="95"/>
+      <c r="C5" s="94"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B6" s="58" t="s">
@@ -10867,22 +10839,22 @@
       </c>
     </row>
     <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="B20" s="92" t="s">
+      <c r="B20" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="C20" s="92"/>
+      <c r="C20" s="100"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="93" t="s">
+      <c r="B21" s="92" t="s">
         <v>170</v>
       </c>
-      <c r="C21" s="93"/>
+      <c r="C21" s="92"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="93" t="s">
         <v>171</v>
       </c>
-      <c r="C23" s="95"/>
+      <c r="C23" s="94"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" s="58" t="s">
@@ -10973,22 +10945,22 @@
       </c>
     </row>
     <row r="38" spans="2:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="B38" s="92" t="s">
+      <c r="B38" s="100" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="92"/>
+      <c r="C38" s="100"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="93" t="s">
+      <c r="B39" s="92" t="s">
         <v>108</v>
       </c>
-      <c r="C39" s="93"/>
+      <c r="C39" s="92"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="94" t="s">
+      <c r="B41" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="95"/>
+      <c r="C41" s="94"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B42" s="58" t="s">
@@ -11079,22 +11051,22 @@
       </c>
     </row>
     <row r="56" spans="2:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="B56" s="92" t="s">
+      <c r="B56" s="100" t="s">
         <v>203</v>
       </c>
-      <c r="C56" s="92"/>
+      <c r="C56" s="100"/>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B57" s="93" t="s">
+      <c r="B57" s="92" t="s">
         <v>204</v>
       </c>
-      <c r="C57" s="93"/>
+      <c r="C57" s="92"/>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B59" s="94" t="s">
+      <c r="B59" s="93" t="s">
         <v>205</v>
       </c>
-      <c r="C59" s="95"/>
+      <c r="C59" s="94"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B60" s="58" t="s">
@@ -11185,31 +11157,31 @@
       </c>
     </row>
     <row r="74" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B74" s="81" t="s">
+      <c r="B74" s="78" t="s">
         <v>273</v>
       </c>
-      <c r="C74" s="82"/>
-      <c r="D74" s="82"/>
-      <c r="E74" s="82"/>
-      <c r="F74" s="82"/>
+      <c r="C74" s="79"/>
+      <c r="D74" s="79"/>
+      <c r="E74" s="79"/>
+      <c r="F74" s="79"/>
     </row>
     <row r="75" spans="2:6" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B75" s="96" t="s">
+      <c r="B75" s="95" t="s">
         <v>274</v>
       </c>
-      <c r="C75" s="97"/>
-      <c r="D75" s="97"/>
-      <c r="E75" s="97"/>
-      <c r="F75" s="97"/>
+      <c r="C75" s="96"/>
+      <c r="D75" s="96"/>
+      <c r="E75" s="96"/>
+      <c r="F75" s="96"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B77" s="98" t="s">
+      <c r="B77" s="97" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="99"/>
-      <c r="D77" s="99"/>
-      <c r="E77" s="99"/>
-      <c r="F77" s="100"/>
+      <c r="C77" s="98"/>
+      <c r="D77" s="98"/>
+      <c r="E77" s="98"/>
+      <c r="F77" s="99"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B78" s="59" t="s">
@@ -11579,21 +11551,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B56:C56"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
